--- a/카드_아키타입/03_앰플·세럼.xlsx
+++ b/카드_아키타입/03_앰플·세럼.xlsx
@@ -1556,7 +1556,7 @@
       <row>128</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1806,7 +1806,7 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="65" name="Image 65" descr="Picture"/>
@@ -5656,7 +5656,7 @@
       <row>493</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="733425"/>
+    <ext cx="1047750" cy="742950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="219" name="Image 219" descr="Picture"/>
@@ -6231,7 +6231,7 @@
       <row>569</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="242" name="Image 242" descr="Picture"/>
@@ -7006,7 +7006,7 @@
       <row>607</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="273" name="Image 273" descr="Picture"/>

--- a/카드_아키타입/03_앰플·세럼.xlsx
+++ b/카드_아키타입/03_앰플·세럼.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40068500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40068500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="40068500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41916350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="52349400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="52349400"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="52349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="52349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>75</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>75</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>75</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>75</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>75</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="65443100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="65443100"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="65443100"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="65443100"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="67290950"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="72237600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="75933300"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="75933300"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="80860900"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>114</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>114</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>114</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="84556600"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90906600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90906600"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90906600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="90906600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>127</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>127</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>127</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>127</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>127</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>127</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>127</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>127</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>127</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>143</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="104813100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>143</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="104813100"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>143</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="104813100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>143</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="104813100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>143</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="106660950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>143</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="106660950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="113030000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="113030000"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="113030000"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="113030000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114877850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114877850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="122466100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="122466100"/>
     <ext cx="1371600" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="122466100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="122466100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124313950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="129057400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="129057400"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="129057400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>183</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="129057400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>183</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="137274300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="137274300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="137274300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="137274300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="140970000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>209</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="147320000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>209</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="147320000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>209</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="147320000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>209</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="147320000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>209</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>209</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>209</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>209</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>223</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="154724100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>223</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="154724100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>223</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="154724100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>223</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="154724100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>223</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>223</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>223</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>223</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="159486600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="159486600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="159486600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>236</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="159486600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>236</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="161334450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="166484300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="166484300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="166484300"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="166484300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>251</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="170180000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="174498000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="174498000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="174498000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="174498000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>264</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="176345850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="180276500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="180276500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="180276500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="180276500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="182124350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>277</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="182124350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="187477400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>293</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="194068700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="194068700"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="194068700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="194068700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>305</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="195916550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>318</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="201269600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>318</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="201269600"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>318</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="201269600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>318</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="201269600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>318</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="203117450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="208064100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>329</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="209911950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>329</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="209911950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216300050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="216300050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="221856300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>349</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>364</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>364</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>364</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>364</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>364</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>364</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>364</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>364</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>364</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="233565700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>364</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="233565700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="238493300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>378</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>392</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="245897400"/>
     <ext cx="1457325" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>392</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>392</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>392</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="251879100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>407</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="260299200"/>
     <ext cx="1809750" cy="1276350"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>416</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>431</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>431</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>431</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>431</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>445</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>445</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>445</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>445</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>461</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="285153100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>461</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="285153100"/>
     <ext cx="1581150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>461</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="285153100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>461</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="285153100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>461</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="287000950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>473</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="292557200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>473</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="292557200"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>486</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="299758100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>486</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="299758100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>486</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="299758100"/>
     <ext cx="1809750" cy="1495425"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>486</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="299758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>486</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>486</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>486</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>486</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>486</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>486</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>486</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>486</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>499</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="312648600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>499</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="312648600"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>499</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="312648600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>499</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="312648600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>499</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>499</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>499</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>511</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="327977500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>511</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="327977500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>511</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="327977500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>511</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="327977500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>511</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>511</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>511</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>511</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>511</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>511</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>511</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>524</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="336600800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>524</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="336600800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>524</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="336600800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>524</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="336600800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="344208100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="344208100"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="344208100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>532</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="344208100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>532</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>532</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>532</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>532</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>550</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="355269800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>550</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="355269800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>550</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="355269800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>558</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="364096300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>574</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="375158000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>574</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="375158000"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>574</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="375158000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>574</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="375158000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>574</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7548,14 +6078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>574</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7573,14 +6098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>574</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7598,14 +6118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>574</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7623,14 +6138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>587</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="386219700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7648,14 +6158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>587</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="386219700"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -7673,14 +6178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>587</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="386219700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7698,14 +6198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>587</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="386219700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7723,14 +6218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>587</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7748,14 +6238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>587</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7773,14 +6258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>587</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7798,14 +6278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>587</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7823,14 +6298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>603</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="400329400"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7848,14 +6318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>613</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7873,14 +6338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>613</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7898,14 +6358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>613</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7923,14 +6378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>613</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7948,14 +6398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>626</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7973,14 +6418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>626</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7998,14 +6438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>626</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8023,14 +6458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>626</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8048,14 +6478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8073,14 +6498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8098,14 +6518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8123,14 +6538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8148,14 +6558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8173,14 +6578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8198,14 +6598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8223,14 +6618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>655</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8248,14 +6638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>655</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8273,14 +6658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>655</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8298,14 +6678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>655</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8323,14 +6698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>664</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8348,14 +6718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>664</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8373,14 +6738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>664</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8398,14 +6758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>664</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8423,14 +6778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>677</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8448,14 +6798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>677</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8473,14 +6818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>677</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8498,14 +6838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>677</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8523,14 +6858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>677</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="446195450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8548,14 +6878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>687</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8573,14 +6898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>687</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8598,14 +6918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>687</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8623,14 +6938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>687</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8648,14 +6958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>699</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8673,14 +6978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>699</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8698,14 +6998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>699</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8723,14 +7018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>699</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8748,14 +7038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>715</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8773,14 +7058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>715</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8798,14 +7078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>715</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8823,14 +7098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>715</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8848,14 +7118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>715</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8873,14 +7138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>715</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8898,14 +7158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>715</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8923,14 +7178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>728</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8948,14 +7198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>728</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8973,14 +7218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>728</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8998,14 +7238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>728</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9023,14 +7258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>742</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9048,14 +7278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>742</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9073,14 +7298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>742</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9098,14 +7318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>742</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9123,14 +7338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>751</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9148,14 +7358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>751</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9173,14 +7378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>751</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9198,14 +7398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>751</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9223,14 +7418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>764</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9248,14 +7438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>764</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9273,14 +7458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>764</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9298,14 +7478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>764</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9323,14 +7498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>764</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9348,14 +7518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>764</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9373,14 +7538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>764</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9398,14 +7558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>764</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9423,14 +7578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>764</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="504952000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9448,14 +7598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>778</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9473,14 +7618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>778</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9498,14 +7638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>778</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9523,14 +7658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>778</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9548,14 +7678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>778</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9573,14 +7698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>778</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9598,14 +7718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>778</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9623,14 +7738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>778</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9648,14 +7758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>778</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="514997700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9673,14 +7778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>778</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="514997700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9698,14 +7798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>793</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9723,14 +7818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>793</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9748,14 +7838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>793</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9773,14 +7858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>793</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9798,14 +7878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>793</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9823,14 +7898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>793</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9848,14 +7918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>793</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9873,14 +7938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>793</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9898,14 +7958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>793</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="527481800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9923,14 +7978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>793</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="527481800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9948,14 +7998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>809</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9973,14 +8018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>809</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9998,14 +8038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>809</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10023,14 +8058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>809</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10048,14 +8078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>822</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10073,14 +8098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>822</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10098,14 +8118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>822</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10123,14 +8138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>822</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10148,14 +8158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>822</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="545928550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10173,14 +8178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>822</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="545928550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10198,14 +8198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>832</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10223,14 +8218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>832</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10248,14 +8238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>832</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10273,14 +8258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>832</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10298,14 +8278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>846</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10323,14 +8298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>846</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10348,14 +8318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>846</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10373,14 +8338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>846</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10398,14 +8358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>859</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10423,14 +8378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>859</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10448,14 +8398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>859</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10473,14 +8418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>859</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10498,14 +8438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>859</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10523,14 +8458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>859</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10548,14 +8478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>859</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10573,7 +8498,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/03_앰플·세럼.xlsx
+++ b/카드_아키타입/03_앰플·세럼.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="6591300"/>
+    <pos x="7391400" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="6591300"/>
+    <pos x="9239250" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="6591300"/>
+    <pos x="11087100" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="6591300"/>
+    <pos x="12934950" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="14401800"/>
+    <pos x="7391400" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="14401800"/>
+    <pos x="9239250" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="14401800"/>
+    <pos x="11087100" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="14401800"/>
+    <pos x="12934950" y="14401800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="16249650"/>
+    <pos x="7391400" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="16249650"/>
+    <pos x="9239250" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="16249650"/>
+    <pos x="11087100" y="16249650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23634700"/>
+    <pos x="7391400" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="23634700"/>
+    <pos x="9239250" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="23634700"/>
+    <pos x="11087100" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="23634700"/>
+    <pos x="12934950" y="23634700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30429200"/>
+    <pos x="7391400" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="30429200"/>
+    <pos x="9239250" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="30429200"/>
+    <pos x="11087100" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="30429200"/>
+    <pos x="12934950" y="30429200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="32277050"/>
+    <pos x="7391400" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="32277050"/>
+    <pos x="9239250" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="32277050"/>
+    <pos x="11087100" y="32277050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40068500"/>
+    <pos x="7391400" y="40068500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40068500"/>
+    <pos x="9239250" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40068500"/>
+    <pos x="11087100" y="40068500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="40068500"/>
+    <pos x="12934950" y="40068500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41916350"/>
+    <pos x="7391400" y="41916350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="52349400"/>
+    <pos x="7391400" y="52349400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="52349400"/>
+    <pos x="9239250" y="52349400"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="52349400"/>
+    <pos x="11087100" y="52349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="52349400"/>
+    <pos x="12934950" y="52349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="54197250"/>
+    <pos x="7391400" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="54197250"/>
+    <pos x="9239250" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="54197250"/>
+    <pos x="11087100" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="54197250"/>
+    <pos x="12934950" y="54197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56045100"/>
+    <pos x="7391400" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56045100"/>
+    <pos x="9239250" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56045100"/>
+    <pos x="11087100" y="56045100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="65443100"/>
+    <pos x="7391400" y="65443100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="65443100"/>
+    <pos x="9239250" y="65443100"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="65443100"/>
+    <pos x="11087100" y="65443100"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="65443100"/>
+    <pos x="12934950" y="65443100"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="67290950"/>
+    <pos x="7391400" y="67290950"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="67290950"/>
+    <pos x="9239250" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="67290950"/>
+    <pos x="11087100" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="67290950"/>
+    <pos x="12934950" y="67290950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69138800"/>
+    <pos x="7391400" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69138800"/>
+    <pos x="9239250" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69138800"/>
+    <pos x="11087100" y="69138800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="72237600"/>
+    <pos x="7391400" y="72237600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="72237600"/>
+    <pos x="9239250" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="72237600"/>
+    <pos x="11087100" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="72237600"/>
+    <pos x="12934950" y="72237600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="74085450"/>
+    <pos x="7391400" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="74085450"/>
+    <pos x="9239250" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="74085450"/>
+    <pos x="11087100" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="74085450"/>
+    <pos x="12934950" y="74085450"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="75933300"/>
+    <pos x="7391400" y="75933300"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="75933300"/>
+    <pos x="9239250" y="75933300"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="80860900"/>
+    <pos x="7391400" y="80860900"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="80860900"/>
+    <pos x="9239250" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="80860900"/>
+    <pos x="11087100" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="80860900"/>
+    <pos x="12934950" y="80860900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82708750"/>
+    <pos x="7391400" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82708750"/>
+    <pos x="9239250" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82708750"/>
+    <pos x="11087100" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="82708750"/>
+    <pos x="12934950" y="82708750"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="84556600"/>
+    <pos x="7391400" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="84556600"/>
+    <pos x="9239250" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="84556600"/>
+    <pos x="11087100" y="84556600"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="84556600"/>
+    <pos x="12934950" y="84556600"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90906600"/>
+    <pos x="7391400" y="90906600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90906600"/>
+    <pos x="9239250" y="90906600"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90906600"/>
+    <pos x="11087100" y="90906600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="90906600"/>
+    <pos x="12934950" y="90906600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="92754450"/>
+    <pos x="7391400" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="92754450"/>
+    <pos x="9239250" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="92754450"/>
+    <pos x="11087100" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="92754450"/>
+    <pos x="12934950" y="92754450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="94602300"/>
+    <pos x="7391400" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="94602300"/>
+    <pos x="9239250" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="94602300"/>
+    <pos x="11087100" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="94602300"/>
+    <pos x="12934950" y="94602300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="96450150"/>
+    <pos x="7391400" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="96450150"/>
+    <pos x="9239250" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="96450150"/>
+    <pos x="11087100" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="96450150"/>
+    <pos x="12934950" y="96450150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="104813100"/>
+    <pos x="7391400" y="104813100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="104813100"/>
+    <pos x="9239250" y="104813100"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="104813100"/>
+    <pos x="11087100" y="104813100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="104813100"/>
+    <pos x="12934950" y="104813100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="106660950"/>
+    <pos x="7391400" y="106660950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="106660950"/>
+    <pos x="9239250" y="106660950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="113030000"/>
+    <pos x="7391400" y="113030000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="113030000"/>
+    <pos x="9239250" y="113030000"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="113030000"/>
+    <pos x="11087100" y="113030000"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="113030000"/>
+    <pos x="12934950" y="113030000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114877850"/>
+    <pos x="7391400" y="114877850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114877850"/>
+    <pos x="9239250" y="114877850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="122466100"/>
+    <pos x="7391400" y="122466100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="122466100"/>
+    <pos x="9239250" y="122466100"/>
     <ext cx="1371600" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="122466100"/>
+    <pos x="11087100" y="122466100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="122466100"/>
+    <pos x="12934950" y="122466100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124313950"/>
+    <pos x="7391400" y="124313950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="129057400"/>
+    <pos x="7391400" y="129057400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="129057400"/>
+    <pos x="9239250" y="129057400"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="129057400"/>
+    <pos x="11087100" y="129057400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="129057400"/>
+    <pos x="12934950" y="129057400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="130905250"/>
+    <pos x="7391400" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="130905250"/>
+    <pos x="9239250" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="130905250"/>
+    <pos x="11087100" y="130905250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="137274300"/>
+    <pos x="7391400" y="137274300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="137274300"/>
+    <pos x="9239250" y="137274300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="137274300"/>
+    <pos x="11087100" y="137274300"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="137274300"/>
+    <pos x="12934950" y="137274300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="139122150"/>
+    <pos x="7391400" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="139122150"/>
+    <pos x="9239250" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="139122150"/>
+    <pos x="11087100" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="139122150"/>
+    <pos x="12934950" y="139122150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="140970000"/>
+    <pos x="7391400" y="140970000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="147320000"/>
+    <pos x="7391400" y="147320000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="147320000"/>
+    <pos x="9239250" y="147320000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="147320000"/>
+    <pos x="11087100" y="147320000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="147320000"/>
+    <pos x="12934950" y="147320000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="149167850"/>
+    <pos x="7391400" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="149167850"/>
+    <pos x="9239250" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="149167850"/>
+    <pos x="11087100" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="149167850"/>
+    <pos x="12934950" y="149167850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="154724100"/>
+    <pos x="7391400" y="154724100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="154724100"/>
+    <pos x="9239250" y="154724100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="154724100"/>
+    <pos x="11087100" y="154724100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="154724100"/>
+    <pos x="12934950" y="154724100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="156571950"/>
+    <pos x="7391400" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="156571950"/>
+    <pos x="9239250" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="156571950"/>
+    <pos x="11087100" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="156571950"/>
+    <pos x="12934950" y="156571950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="159486600"/>
+    <pos x="7391400" y="159486600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="159486600"/>
+    <pos x="9239250" y="159486600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="159486600"/>
+    <pos x="11087100" y="159486600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="159486600"/>
+    <pos x="12934950" y="159486600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="161334450"/>
+    <pos x="7391400" y="161334450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="166484300"/>
+    <pos x="7391400" y="166484300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="166484300"/>
+    <pos x="9239250" y="166484300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="166484300"/>
+    <pos x="11087100" y="166484300"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="166484300"/>
+    <pos x="12934950" y="166484300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="168332150"/>
+    <pos x="7391400" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="168332150"/>
+    <pos x="9239250" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="168332150"/>
+    <pos x="11087100" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="168332150"/>
+    <pos x="12934950" y="168332150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="170180000"/>
+    <pos x="7391400" y="170180000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="174498000"/>
+    <pos x="7391400" y="174498000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="174498000"/>
+    <pos x="9239250" y="174498000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="174498000"/>
+    <pos x="11087100" y="174498000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="174498000"/>
+    <pos x="12934950" y="174498000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="176345850"/>
+    <pos x="7391400" y="176345850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="180276500"/>
+    <pos x="7391400" y="180276500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="180276500"/>
+    <pos x="9239250" y="180276500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="180276500"/>
+    <pos x="11087100" y="180276500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="180276500"/>
+    <pos x="12934950" y="180276500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="182124350"/>
+    <pos x="7391400" y="182124350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="182124350"/>
+    <pos x="9239250" y="182124350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="187477400"/>
+    <pos x="7391400" y="187477400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="187477400"/>
+    <pos x="9239250" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="187477400"/>
+    <pos x="11087100" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="187477400"/>
+    <pos x="12934950" y="187477400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="194068700"/>
+    <pos x="7391400" y="194068700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="194068700"/>
+    <pos x="9239250" y="194068700"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="194068700"/>
+    <pos x="11087100" y="194068700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="194068700"/>
+    <pos x="12934950" y="194068700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="195916550"/>
+    <pos x="7391400" y="195916550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="201269600"/>
+    <pos x="7391400" y="201269600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="201269600"/>
+    <pos x="9239250" y="201269600"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="201269600"/>
+    <pos x="11087100" y="201269600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="201269600"/>
+    <pos x="12934950" y="201269600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="203117450"/>
+    <pos x="7391400" y="203117450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="208064100"/>
+    <pos x="7391400" y="208064100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="208064100"/>
+    <pos x="9239250" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="208064100"/>
+    <pos x="11087100" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="208064100"/>
+    <pos x="12934950" y="208064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="209911950"/>
+    <pos x="7391400" y="209911950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="209911950"/>
+    <pos x="9239250" y="209911950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="214452200"/>
+    <pos x="7391400" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="214452200"/>
+    <pos x="9239250" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="214452200"/>
+    <pos x="11087100" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="214452200"/>
+    <pos x="12934950" y="214452200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216300050"/>
+    <pos x="7391400" y="216300050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="216300050"/>
+    <pos x="9239250" y="216300050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="221856300"/>
+    <pos x="7391400" y="221856300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="221856300"/>
+    <pos x="9239250" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="221856300"/>
+    <pos x="11087100" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="221856300"/>
+    <pos x="12934950" y="221856300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="229870000"/>
+    <pos x="7391400" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="229870000"/>
+    <pos x="9239250" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="229870000"/>
+    <pos x="11087100" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="229870000"/>
+    <pos x="12934950" y="229870000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="231717850"/>
+    <pos x="7391400" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="231717850"/>
+    <pos x="9239250" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="231717850"/>
+    <pos x="11087100" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="231717850"/>
+    <pos x="12934950" y="231717850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="233565700"/>
+    <pos x="7391400" y="233565700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="233565700"/>
+    <pos x="9239250" y="233565700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="238493300"/>
+    <pos x="7391400" y="238493300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="238493300"/>
+    <pos x="9239250" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="238493300"/>
+    <pos x="11087100" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="238493300"/>
+    <pos x="12934950" y="238493300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="245897400"/>
+    <pos x="7391400" y="245897400"/>
     <ext cx="1457325" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="245897400"/>
+    <pos x="9239250" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="245897400"/>
+    <pos x="11087100" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="245897400"/>
+    <pos x="12934950" y="245897400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="251879100"/>
+    <pos x="7391400" y="251879100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="251879100"/>
+    <pos x="9239250" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="251879100"/>
+    <pos x="11087100" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="251879100"/>
+    <pos x="12934950" y="251879100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="260299200"/>
+    <pos x="7391400" y="260299200"/>
     <ext cx="1809750" cy="1276350"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="260299200"/>
+    <pos x="9239250" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="260299200"/>
+    <pos x="11087100" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="260299200"/>
+    <pos x="12934950" y="260299200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="264858500"/>
+    <pos x="7391400" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="264858500"/>
+    <pos x="9239250" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="264858500"/>
+    <pos x="11087100" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="264858500"/>
+    <pos x="12934950" y="264858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="273075400"/>
+    <pos x="7391400" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="273075400"/>
+    <pos x="9239250" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="273075400"/>
+    <pos x="11087100" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="273075400"/>
+    <pos x="12934950" y="273075400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="274923250"/>
+    <pos x="7391400" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="274923250"/>
+    <pos x="9239250" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="274923250"/>
+    <pos x="11087100" y="274923250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="285153100"/>
+    <pos x="7391400" y="285153100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="285153100"/>
+    <pos x="9239250" y="285153100"/>
     <ext cx="1581150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="285153100"/>
+    <pos x="11087100" y="285153100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="285153100"/>
+    <pos x="12934950" y="285153100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="287000950"/>
+    <pos x="7391400" y="287000950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="292557200"/>
+    <pos x="7391400" y="292557200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="292557200"/>
+    <pos x="9239250" y="292557200"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="299758100"/>
+    <pos x="7391400" y="299758100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="299758100"/>
+    <pos x="9239250" y="299758100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="299758100"/>
+    <pos x="11087100" y="299758100"/>
     <ext cx="1809750" cy="1495425"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="299758100"/>
+    <pos x="12934950" y="299758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="301605950"/>
+    <pos x="7391400" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="301605950"/>
+    <pos x="9239250" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="301605950"/>
+    <pos x="11087100" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="301605950"/>
+    <pos x="12934950" y="301605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="303453800"/>
+    <pos x="7391400" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="303453800"/>
+    <pos x="9239250" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="303453800"/>
+    <pos x="11087100" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="303453800"/>
+    <pos x="12934950" y="303453800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="312648600"/>
+    <pos x="7391400" y="312648600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="312648600"/>
+    <pos x="9239250" y="312648600"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="312648600"/>
+    <pos x="11087100" y="312648600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="312648600"/>
+    <pos x="12934950" y="312648600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="314496450"/>
+    <pos x="7391400" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="314496450"/>
+    <pos x="9239250" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="314496450"/>
+    <pos x="11087100" y="314496450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="327977500"/>
+    <pos x="7391400" y="327977500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="327977500"/>
+    <pos x="9239250" y="327977500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="327977500"/>
+    <pos x="11087100" y="327977500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="327977500"/>
+    <pos x="12934950" y="327977500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="329825350"/>
+    <pos x="7391400" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="329825350"/>
+    <pos x="9239250" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="329825350"/>
+    <pos x="11087100" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="329825350"/>
+    <pos x="12934950" y="329825350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="331673200"/>
+    <pos x="7391400" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="331673200"/>
+    <pos x="9239250" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="331673200"/>
+    <pos x="11087100" y="331673200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="336600800"/>
+    <pos x="7391400" y="336600800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="336600800"/>
+    <pos x="9239250" y="336600800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="336600800"/>
+    <pos x="11087100" y="336600800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="336600800"/>
+    <pos x="12934950" y="336600800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="344208100"/>
+    <pos x="7391400" y="344208100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="344208100"/>
+    <pos x="9239250" y="344208100"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="344208100"/>
+    <pos x="11087100" y="344208100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="344208100"/>
+    <pos x="12934950" y="344208100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="346055950"/>
+    <pos x="7391400" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="346055950"/>
+    <pos x="9239250" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="346055950"/>
+    <pos x="11087100" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="346055950"/>
+    <pos x="12934950" y="346055950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="347903800"/>
+    <pos x="7391400" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="347903800"/>
+    <pos x="9239250" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="347903800"/>
+    <pos x="11087100" y="347903800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="355269800"/>
+    <pos x="7391400" y="355269800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="355269800"/>
+    <pos x="9239250" y="355269800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="355269800"/>
+    <pos x="11087100" y="355269800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="364096300"/>
+    <pos x="7391400" y="364096300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="375158000"/>
+    <pos x="7391400" y="375158000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="375158000"/>
+    <pos x="9239250" y="375158000"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="375158000"/>
+    <pos x="11087100" y="375158000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="375158000"/>
+    <pos x="12934950" y="375158000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="377005850"/>
+    <pos x="7391400" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="377005850"/>
+    <pos x="9239250" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="377005850"/>
+    <pos x="11087100" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="377005850"/>
+    <pos x="12934950" y="377005850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="386219700"/>
+    <pos x="7391400" y="386219700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="386219700"/>
+    <pos x="9239250" y="386219700"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="386219700"/>
+    <pos x="11087100" y="386219700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="386219700"/>
+    <pos x="12934950" y="386219700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="388067550"/>
+    <pos x="7391400" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="388067550"/>
+    <pos x="9239250" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="388067550"/>
+    <pos x="11087100" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="388067550"/>
+    <pos x="12934950" y="388067550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="400329400"/>
+    <pos x="7391400" y="400329400"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="405498300"/>
+    <pos x="7391400" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="405498300"/>
+    <pos x="9239250" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="405498300"/>
+    <pos x="11087100" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="405498300"/>
+    <pos x="12934950" y="405498300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="413105600"/>
+    <pos x="7391400" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="413105600"/>
+    <pos x="9239250" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="413105600"/>
+    <pos x="11087100" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="413105600"/>
+    <pos x="12934950" y="413105600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="420509700"/>
+    <pos x="7391400" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="420509700"/>
+    <pos x="9239250" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="420509700"/>
+    <pos x="11087100" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="420509700"/>
+    <pos x="12934950" y="420509700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="422357550"/>
+    <pos x="7391400" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="422357550"/>
+    <pos x="9239250" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="422357550"/>
+    <pos x="11087100" y="422357550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="429742600"/>
+    <pos x="7391400" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="429742600"/>
+    <pos x="9239250" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="429742600"/>
+    <pos x="11087100" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="429742600"/>
+    <pos x="12934950" y="429742600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="436740300"/>
+    <pos x="7391400" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="436740300"/>
+    <pos x="9239250" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="436740300"/>
+    <pos x="11087100" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="436740300"/>
+    <pos x="12934950" y="436740300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="444347600"/>
+    <pos x="7391400" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="444347600"/>
+    <pos x="9239250" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="444347600"/>
+    <pos x="11087100" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="444347600"/>
+    <pos x="12934950" y="444347600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="446195450"/>
+    <pos x="7391400" y="446195450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6880,7 +6880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="456018900"/>
+    <pos x="7391400" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6900,7 +6900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="456018900"/>
+    <pos x="9239250" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6920,7 +6920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="456018900"/>
+    <pos x="11087100" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6940,7 +6940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="456018900"/>
+    <pos x="12934950" y="456018900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6960,7 +6960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="463423000"/>
+    <pos x="7391400" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6980,7 +6980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="463423000"/>
+    <pos x="9239250" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7000,7 +7000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="463423000"/>
+    <pos x="11087100" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7020,7 +7020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="463423000"/>
+    <pos x="12934950" y="463423000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7040,7 +7040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="472249500"/>
+    <pos x="7391400" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7060,7 +7060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="472249500"/>
+    <pos x="9239250" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7080,7 +7080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="472249500"/>
+    <pos x="11087100" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7100,7 +7100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="472249500"/>
+    <pos x="12934950" y="472249500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7120,7 +7120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="474097350"/>
+    <pos x="7391400" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7140,7 +7140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="474097350"/>
+    <pos x="9239250" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7160,7 +7160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="474097350"/>
+    <pos x="11087100" y="474097350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7180,7 +7180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="480263200"/>
+    <pos x="7391400" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7200,7 +7200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="480263200"/>
+    <pos x="9239250" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7220,7 +7220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="480263200"/>
+    <pos x="11087100" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7240,7 +7240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="480263200"/>
+    <pos x="12934950" y="480263200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7260,7 +7260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="487870500"/>
+    <pos x="7391400" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7280,7 +7280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="487870500"/>
+    <pos x="9239250" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7300,7 +7300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="487870500"/>
+    <pos x="11087100" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7320,7 +7320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="487870500"/>
+    <pos x="12934950" y="487870500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7340,7 +7340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="493649000"/>
+    <pos x="7391400" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7360,7 +7360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="493649000"/>
+    <pos x="9239250" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7380,7 +7380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="493649000"/>
+    <pos x="11087100" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7400,7 +7400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="493649000"/>
+    <pos x="12934950" y="493649000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7420,7 +7420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="501256300"/>
+    <pos x="7391400" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7440,7 +7440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="501256300"/>
+    <pos x="9239250" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7460,7 +7460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="501256300"/>
+    <pos x="11087100" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7480,7 +7480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="501256300"/>
+    <pos x="12934950" y="501256300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7500,7 +7500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="503104150"/>
+    <pos x="7391400" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7520,7 +7520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="503104150"/>
+    <pos x="9239250" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7540,7 +7540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="503104150"/>
+    <pos x="11087100" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7560,7 +7560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="503104150"/>
+    <pos x="12934950" y="503104150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7580,7 +7580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="504952000"/>
+    <pos x="7391400" y="504952000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7600,7 +7600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="511302000"/>
+    <pos x="7391400" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7620,7 +7620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="511302000"/>
+    <pos x="9239250" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7640,7 +7640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="511302000"/>
+    <pos x="11087100" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7660,7 +7660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="511302000"/>
+    <pos x="12934950" y="511302000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7680,7 +7680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="513149850"/>
+    <pos x="7391400" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7700,7 +7700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="513149850"/>
+    <pos x="9239250" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7720,7 +7720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="513149850"/>
+    <pos x="11087100" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7740,7 +7740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="513149850"/>
+    <pos x="12934950" y="513149850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7760,7 +7760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="514997700"/>
+    <pos x="7391400" y="514997700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7780,7 +7780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="514997700"/>
+    <pos x="9239250" y="514997700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7800,7 +7800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="523786100"/>
+    <pos x="7391400" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7820,7 +7820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="523786100"/>
+    <pos x="9239250" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7840,7 +7840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="523786100"/>
+    <pos x="11087100" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7860,7 +7860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="523786100"/>
+    <pos x="12934950" y="523786100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7880,7 +7880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="525633950"/>
+    <pos x="7391400" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7900,7 +7900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="525633950"/>
+    <pos x="9239250" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7920,7 +7920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="525633950"/>
+    <pos x="11087100" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7940,7 +7940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="525633950"/>
+    <pos x="12934950" y="525633950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7960,7 +7960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="527481800"/>
+    <pos x="7391400" y="527481800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7980,7 +7980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="527481800"/>
+    <pos x="9239250" y="527481800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8000,7 +8000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="535051000"/>
+    <pos x="7391400" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8020,7 +8020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="535051000"/>
+    <pos x="9239250" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8040,7 +8040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="535051000"/>
+    <pos x="11087100" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8060,7 +8060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="535051000"/>
+    <pos x="12934950" y="535051000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8080,7 +8080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="544080700"/>
+    <pos x="7391400" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8100,7 +8100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="544080700"/>
+    <pos x="9239250" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8120,7 +8120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="544080700"/>
+    <pos x="11087100" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8140,7 +8140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="544080700"/>
+    <pos x="12934950" y="544080700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8160,7 +8160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="545928550"/>
+    <pos x="7391400" y="545928550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8180,7 +8180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="545928550"/>
+    <pos x="9239250" y="545928550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8200,7 +8200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="557377600"/>
+    <pos x="7391400" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8220,7 +8220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="557377600"/>
+    <pos x="9239250" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8240,7 +8240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="557377600"/>
+    <pos x="11087100" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8260,7 +8260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="557377600"/>
+    <pos x="12934950" y="557377600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8280,7 +8280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="566000900"/>
+    <pos x="7391400" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8300,7 +8300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="566000900"/>
+    <pos x="9239250" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8320,7 +8320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="566000900"/>
+    <pos x="11087100" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8340,7 +8340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="566000900"/>
+    <pos x="12934950" y="566000900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8360,7 +8360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="573608200"/>
+    <pos x="7391400" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8380,7 +8380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="573608200"/>
+    <pos x="9239250" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8400,7 +8400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="573608200"/>
+    <pos x="11087100" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8420,7 +8420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="573608200"/>
+    <pos x="12934950" y="573608200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8440,7 +8440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="575456050"/>
+    <pos x="7391400" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8460,7 +8460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="575456050"/>
+    <pos x="9239250" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8480,7 +8480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="575456050"/>
+    <pos x="11087100" y="575456050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8798,7 +8798,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/03_앰플·세럼.xlsx
+++ b/카드_아키타입/03_앰플·세럼.xlsx
@@ -748,7 +748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34823400"/>
+    <pos x="7848600" y="34620200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -768,7 +768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="34823400"/>
+    <pos x="9696450" y="34620200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -788,7 +788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="34823400"/>
+    <pos x="11544300" y="34620200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -808,7 +808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="34823400"/>
+    <pos x="13392150" y="34620200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -828,7 +828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="36671250"/>
+    <pos x="7848600" y="36468050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,7 +848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="36671250"/>
+    <pos x="9696450" y="36468050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -868,7 +868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="36671250"/>
+    <pos x="11544300" y="36468050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -888,7 +888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45453300"/>
+    <pos x="7848600" y="45250100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -908,7 +908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45453300"/>
+    <pos x="9696450" y="45250100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -928,7 +928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45453300"/>
+    <pos x="11544300" y="45250100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -948,7 +948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45453300"/>
+    <pos x="13392150" y="45250100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -968,7 +968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47301150"/>
+    <pos x="7848600" y="47097950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -988,7 +988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="58115200"/>
+    <pos x="7848600" y="57912000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1008,7 +1008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="58115200"/>
+    <pos x="9696450" y="57912000"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -1028,7 +1028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="58115200"/>
+    <pos x="11544300" y="57912000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1048,7 +1048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="58115200"/>
+    <pos x="13392150" y="57912000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1068,7 +1068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="59963050"/>
+    <pos x="7848600" y="59759850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1088,7 +1088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="59963050"/>
+    <pos x="9696450" y="59759850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1108,7 +1108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="59963050"/>
+    <pos x="11544300" y="59759850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1128,7 +1128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="59963050"/>
+    <pos x="13392150" y="59759850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1148,7 +1148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61810900"/>
+    <pos x="7848600" y="61607700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1168,7 +1168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61810900"/>
+    <pos x="9696450" y="61607700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1188,7 +1188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="61810900"/>
+    <pos x="11544300" y="61607700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1208,7 +1208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="71793100"/>
+    <pos x="7848600" y="71589900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1228,7 +1228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="71793100"/>
+    <pos x="9696450" y="71589900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1248,7 +1248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="71793100"/>
+    <pos x="11544300" y="71589900"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1268,7 +1268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="71793100"/>
+    <pos x="13392150" y="71589900"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1288,7 +1288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="73640950"/>
+    <pos x="7848600" y="73437750"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1308,7 +1308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="73640950"/>
+    <pos x="9696450" y="73437750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1328,7 +1328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="73640950"/>
+    <pos x="11544300" y="73437750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1348,7 +1348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="73640950"/>
+    <pos x="13392150" y="73437750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1368,7 +1368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="75488800"/>
+    <pos x="7848600" y="75285600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1388,7 +1388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="75488800"/>
+    <pos x="9696450" y="75285600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1408,7 +1408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="75488800"/>
+    <pos x="11544300" y="75285600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1428,7 +1428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78968600"/>
+    <pos x="7848600" y="78765400"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1448,7 +1448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78968600"/>
+    <pos x="9696450" y="78765400"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1468,7 +1468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78968600"/>
+    <pos x="11544300" y="78765400"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1488,7 +1488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78968600"/>
+    <pos x="13392150" y="78765400"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1508,7 +1508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80816450"/>
+    <pos x="7848600" y="80613250"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1528,7 +1528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80816450"/>
+    <pos x="9696450" y="80613250"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1548,7 +1548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80816450"/>
+    <pos x="11544300" y="80613250"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1568,7 +1568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="80816450"/>
+    <pos x="13392150" y="80613250"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1588,7 +1588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="82664300"/>
+    <pos x="7848600" y="82461100"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1608,7 +1608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="82664300"/>
+    <pos x="9696450" y="82461100"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1628,7 +1628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87769700"/>
+    <pos x="7848600" y="87566500"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1648,7 +1648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87769700"/>
+    <pos x="9696450" y="87566500"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1668,7 +1668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87769700"/>
+    <pos x="11544300" y="87566500"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1688,7 +1688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="87769700"/>
+    <pos x="13392150" y="87566500"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1708,7 +1708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="89617550"/>
+    <pos x="7848600" y="89414350"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1728,7 +1728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="89617550"/>
+    <pos x="9696450" y="89414350"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1748,7 +1748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="89617550"/>
+    <pos x="11544300" y="89414350"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1768,7 +1768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="89617550"/>
+    <pos x="13392150" y="89414350"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1788,7 +1788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91465400"/>
+    <pos x="7848600" y="91262200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1808,7 +1808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="91465400"/>
+    <pos x="9696450" y="91262200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1828,7 +1828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="91465400"/>
+    <pos x="11544300" y="91262200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1848,7 +1848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="91465400"/>
+    <pos x="13392150" y="91262200"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1868,7 +1868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="98399600"/>
+    <pos x="7848600" y="97993200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1888,7 +1888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="98399600"/>
+    <pos x="9696450" y="97993200"/>
     <ext cx="1809750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1908,7 +1908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="98399600"/>
+    <pos x="11544300" y="97993200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1928,7 +1928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="98399600"/>
+    <pos x="13392150" y="97993200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1948,7 +1948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100247450"/>
+    <pos x="7848600" y="99841050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1968,7 +1968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="100247450"/>
+    <pos x="9696450" y="99841050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1988,7 +1988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="100247450"/>
+    <pos x="11544300" y="99841050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2008,7 +2008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="100247450"/>
+    <pos x="13392150" y="99841050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2028,7 +2028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="102095300"/>
+    <pos x="7848600" y="101688900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,7 +2048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="102095300"/>
+    <pos x="9696450" y="101688900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2068,7 +2068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="102095300"/>
+    <pos x="11544300" y="101688900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2088,7 +2088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="102095300"/>
+    <pos x="13392150" y="101688900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2108,7 +2108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="103943150"/>
+    <pos x="7848600" y="103536750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2128,7 +2128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="103943150"/>
+    <pos x="9696450" y="103536750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,7 +2148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="103943150"/>
+    <pos x="11544300" y="103536750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2168,7 +2168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="103943150"/>
+    <pos x="13392150" y="103536750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2188,7 +2188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="113093500"/>
+    <pos x="7848600" y="112687100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2208,7 +2208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="113093500"/>
+    <pos x="9696450" y="112687100"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2228,7 +2228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="113093500"/>
+    <pos x="11544300" y="112687100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2248,7 +2248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="113093500"/>
+    <pos x="13392150" y="112687100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2268,7 +2268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="114941350"/>
+    <pos x="7848600" y="114534950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2288,7 +2288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="114941350"/>
+    <pos x="9696450" y="114534950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2308,7 +2308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="121691400"/>
+    <pos x="7848600" y="121081800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2328,7 +2328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="121691400"/>
+    <pos x="9696450" y="121081800"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,7 +2348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="121691400"/>
+    <pos x="11544300" y="121081800"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -2368,7 +2368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="121691400"/>
+    <pos x="13392150" y="121081800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2388,7 +2388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="123539250"/>
+    <pos x="7848600" y="122929650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2408,7 +2408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="123539250"/>
+    <pos x="9696450" y="122929650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2428,7 +2428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="131711700"/>
+    <pos x="7848600" y="131102100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2448,7 +2448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="131711700"/>
+    <pos x="9696450" y="131102100"/>
     <ext cx="1371600" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2468,7 +2468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="131711700"/>
+    <pos x="11544300" y="131102100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2488,7 +2488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="131711700"/>
+    <pos x="13392150" y="131102100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2508,7 +2508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="133559550"/>
+    <pos x="7848600" y="132949950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2528,7 +2528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="139090400"/>
+    <pos x="7848600" y="138480800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2548,7 +2548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="139090400"/>
+    <pos x="9696450" y="138480800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2568,7 +2568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="139090400"/>
+    <pos x="11544300" y="138480800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2588,7 +2588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="139090400"/>
+    <pos x="13392150" y="138480800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2608,7 +2608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="140938250"/>
+    <pos x="7848600" y="140328650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2628,7 +2628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="140938250"/>
+    <pos x="9696450" y="140328650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2648,7 +2648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="140938250"/>
+    <pos x="11544300" y="140328650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2668,7 +2668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="148094700"/>
+    <pos x="7848600" y="147485100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2688,7 +2688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="148094700"/>
+    <pos x="9696450" y="147485100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2708,7 +2708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="148094700"/>
+    <pos x="11544300" y="147485100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2728,7 +2728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="148094700"/>
+    <pos x="13392150" y="147485100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2748,7 +2748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="149942550"/>
+    <pos x="7848600" y="149332950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2768,7 +2768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="149942550"/>
+    <pos x="9696450" y="149332950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2788,7 +2788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="149942550"/>
+    <pos x="11544300" y="149332950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2808,7 +2808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="149942550"/>
+    <pos x="13392150" y="149332950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2828,7 +2828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151790400"/>
+    <pos x="7848600" y="151180800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2848,7 +2848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="159131000"/>
+    <pos x="7848600" y="158318200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2868,7 +2868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="159131000"/>
+    <pos x="9696450" y="158318200"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2888,7 +2888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="159131000"/>
+    <pos x="11544300" y="158318200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2908,7 +2908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="159131000"/>
+    <pos x="13392150" y="158318200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2928,7 +2928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="160978850"/>
+    <pos x="7848600" y="160166050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2948,7 +2948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="160978850"/>
+    <pos x="9696450" y="160166050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2968,7 +2968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="160978850"/>
+    <pos x="11544300" y="160166050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2988,7 +2988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="160978850"/>
+    <pos x="13392150" y="160166050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3008,7 +3008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="167322500"/>
+    <pos x="7848600" y="166306500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3028,7 +3028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="167322500"/>
+    <pos x="9696450" y="166306500"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,7 +3048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="167322500"/>
+    <pos x="11544300" y="166306500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3068,7 +3068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="167322500"/>
+    <pos x="13392150" y="166306500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3088,7 +3088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="169170350"/>
+    <pos x="7848600" y="168154350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3108,7 +3108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="169170350"/>
+    <pos x="9696450" y="168154350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3128,7 +3128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="169170350"/>
+    <pos x="11544300" y="168154350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3148,7 +3148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="169170350"/>
+    <pos x="13392150" y="168154350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3168,7 +3168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="172262800"/>
+    <pos x="7848600" y="171246800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3188,7 +3188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="172262800"/>
+    <pos x="9696450" y="171246800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3208,7 +3208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="172262800"/>
+    <pos x="11544300" y="171246800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3228,7 +3228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="172262800"/>
+    <pos x="13392150" y="171246800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3248,7 +3248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="174110650"/>
+    <pos x="7848600" y="173094650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3268,7 +3268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179844700"/>
+    <pos x="7848600" y="178828700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3288,7 +3288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179844700"/>
+    <pos x="9696450" y="178828700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3308,7 +3308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179844700"/>
+    <pos x="11544300" y="178828700"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3328,7 +3328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179844700"/>
+    <pos x="13392150" y="178828700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3348,7 +3348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="181692550"/>
+    <pos x="7848600" y="180676550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3368,7 +3368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="181692550"/>
+    <pos x="9696450" y="180676550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3388,7 +3388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="181692550"/>
+    <pos x="11544300" y="180676550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3408,7 +3408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="181692550"/>
+    <pos x="13392150" y="180676550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3428,7 +3428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="183540400"/>
+    <pos x="7848600" y="182524400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3448,7 +3448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="188442600"/>
+    <pos x="7848600" y="187426600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3468,7 +3468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="188442600"/>
+    <pos x="9696450" y="187426600"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3488,7 +3488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="188442600"/>
+    <pos x="11544300" y="187426600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3508,7 +3508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="188442600"/>
+    <pos x="13392150" y="187426600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3528,7 +3528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="190290450"/>
+    <pos x="7848600" y="189274450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3548,7 +3548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="195414900"/>
+    <pos x="7848600" y="194398900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3568,7 +3568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="195414900"/>
+    <pos x="9696450" y="194398900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3588,7 +3588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="195414900"/>
+    <pos x="11544300" y="194398900"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3608,7 +3608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="195414900"/>
+    <pos x="13392150" y="194398900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3628,7 +3628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="197262750"/>
+    <pos x="7848600" y="196246750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3648,7 +3648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="197262750"/>
+    <pos x="9696450" y="196246750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3668,7 +3668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="203403200"/>
+    <pos x="7848600" y="202387200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3688,7 +3688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="203403200"/>
+    <pos x="9696450" y="202387200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3708,7 +3708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="203403200"/>
+    <pos x="11544300" y="202387200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3728,7 +3728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="203403200"/>
+    <pos x="13392150" y="202387200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3748,7 +3748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="210985100"/>
+    <pos x="7848600" y="209969100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3768,7 +3768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="210985100"/>
+    <pos x="9696450" y="209969100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3788,7 +3788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="210985100"/>
+    <pos x="11544300" y="209969100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3808,7 +3808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="210985100"/>
+    <pos x="13392150" y="209969100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3828,7 +3828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="212832950"/>
+    <pos x="7848600" y="211816950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3848,7 +3848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="218973400"/>
+    <pos x="7848600" y="217957400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3868,7 +3868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="218973400"/>
+    <pos x="9696450" y="217957400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3888,7 +3888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="218973400"/>
+    <pos x="11544300" y="217957400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3908,7 +3908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="218973400"/>
+    <pos x="13392150" y="217957400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3928,7 +3928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="220821250"/>
+    <pos x="7848600" y="219805250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3948,7 +3948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="226352100"/>
+    <pos x="7848600" y="225336100"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3968,7 +3968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="226352100"/>
+    <pos x="9696450" y="225336100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3988,7 +3988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="226352100"/>
+    <pos x="11544300" y="225336100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4008,7 +4008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="226352100"/>
+    <pos x="13392150" y="225336100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4028,7 +4028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="228199950"/>
+    <pos x="7848600" y="227183950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,7 +4048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="228199950"/>
+    <pos x="9696450" y="227183950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4068,7 +4068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="232918000"/>
+    <pos x="7848600" y="231902000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4088,7 +4088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="232918000"/>
+    <pos x="9696450" y="231902000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4108,7 +4108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="232918000"/>
+    <pos x="11544300" y="231902000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4128,7 +4128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="232918000"/>
+    <pos x="13392150" y="231902000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,7 +4148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="234765850"/>
+    <pos x="7848600" y="233749850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4168,7 +4168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="234765850"/>
+    <pos x="9696450" y="233749850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4188,7 +4188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="240703100"/>
+    <pos x="7848600" y="239687100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4208,7 +4208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="240703100"/>
+    <pos x="9696450" y="239687100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4228,7 +4228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="240703100"/>
+    <pos x="11544300" y="239687100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4248,7 +4248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="240703100"/>
+    <pos x="13392150" y="239687100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4268,7 +4268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="249707400"/>
+    <pos x="7848600" y="248691400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4288,7 +4288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="249707400"/>
+    <pos x="9696450" y="248691400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4308,7 +4308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="249707400"/>
+    <pos x="11544300" y="248691400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4328,7 +4328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="249707400"/>
+    <pos x="13392150" y="248691400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,7 +4348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="251555250"/>
+    <pos x="7848600" y="250539250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4368,7 +4368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="251555250"/>
+    <pos x="9696450" y="250539250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4388,7 +4388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="251555250"/>
+    <pos x="11544300" y="250539250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4408,7 +4408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="251555250"/>
+    <pos x="13392150" y="250539250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4428,7 +4428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="253403100"/>
+    <pos x="7848600" y="252387100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,7 +4448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="253403100"/>
+    <pos x="9696450" y="252387100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4468,7 +4468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="259321300"/>
+    <pos x="7848600" y="258305300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4488,7 +4488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="259321300"/>
+    <pos x="9696450" y="258305300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4508,7 +4508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="259321300"/>
+    <pos x="11544300" y="258305300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4528,7 +4528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="259321300"/>
+    <pos x="13392150" y="258305300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4548,7 +4548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="267512800"/>
+    <pos x="7848600" y="266496800"/>
     <ext cx="1457325" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4568,7 +4568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="267512800"/>
+    <pos x="9696450" y="266496800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4588,7 +4588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="267512800"/>
+    <pos x="11544300" y="266496800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4608,7 +4608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="267512800"/>
+    <pos x="13392150" y="266496800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4628,7 +4628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="274485100"/>
+    <pos x="7848600" y="273469100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,7 +4648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="274485100"/>
+    <pos x="9696450" y="273469100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4668,7 +4668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="274485100"/>
+    <pos x="11544300" y="273469100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4688,7 +4688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="274485100"/>
+    <pos x="13392150" y="273469100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4708,7 +4708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="283489400"/>
+    <pos x="7848600" y="282270200"/>
     <ext cx="1809750" cy="1276350"/>
     <pic>
       <nvPicPr>
@@ -4728,7 +4728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="283489400"/>
+    <pos x="9696450" y="282270200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4748,7 +4748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="283489400"/>
+    <pos x="11544300" y="282270200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4768,7 +4768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="283489400"/>
+    <pos x="13392150" y="282270200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4788,7 +4788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="289242500"/>
+    <pos x="7848600" y="288023300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4808,7 +4808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="289242500"/>
+    <pos x="9696450" y="288023300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4828,7 +4828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="289242500"/>
+    <pos x="11544300" y="288023300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,7 +4848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="289242500"/>
+    <pos x="13392150" y="288023300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4868,7 +4868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="298653200"/>
+    <pos x="7848600" y="297434000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4888,7 +4888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="298653200"/>
+    <pos x="9696450" y="297434000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4908,7 +4908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="298653200"/>
+    <pos x="11544300" y="297434000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4928,7 +4928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="298653200"/>
+    <pos x="13392150" y="297434000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,7 +4948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="300501050"/>
+    <pos x="7848600" y="299281850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4968,7 +4968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="300501050"/>
+    <pos x="9696450" y="299281850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4988,7 +4988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="300501050"/>
+    <pos x="11544300" y="299281850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5008,7 +5008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="311721500"/>
+    <pos x="7848600" y="310502300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5028,7 +5028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="311721500"/>
+    <pos x="9696450" y="310502300"/>
     <ext cx="1581150" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,7 +5048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="311721500"/>
+    <pos x="11544300" y="310502300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5068,7 +5068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="311721500"/>
+    <pos x="13392150" y="310502300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5088,7 +5088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="313569350"/>
+    <pos x="7848600" y="312350150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5108,7 +5108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="320116200"/>
+    <pos x="7848600" y="318897000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5128,7 +5128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="320116200"/>
+    <pos x="9696450" y="318897000"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -5148,7 +5148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="327901300"/>
+    <pos x="7848600" y="326682100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5168,7 +5168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="327901300"/>
+    <pos x="9696450" y="326682100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -5188,7 +5188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="327901300"/>
+    <pos x="11544300" y="326682100"/>
     <ext cx="1809750" cy="1495425"/>
     <pic>
       <nvPicPr>
@@ -5208,7 +5208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="327901300"/>
+    <pos x="13392150" y="326682100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5228,7 +5228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="329749150"/>
+    <pos x="7848600" y="328529950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5248,7 +5248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="329749150"/>
+    <pos x="9696450" y="328529950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5268,7 +5268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="329749150"/>
+    <pos x="11544300" y="328529950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5288,7 +5288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="329749150"/>
+    <pos x="13392150" y="328529950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5308,7 +5308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="331597000"/>
+    <pos x="7848600" y="330377800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5328,7 +5328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="331597000"/>
+    <pos x="9696450" y="330377800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5348,7 +5348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="331597000"/>
+    <pos x="11544300" y="330377800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5368,7 +5368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="331597000"/>
+    <pos x="13392150" y="330377800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5388,7 +5388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="340969600"/>
+    <pos x="7848600" y="339750400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5408,7 +5408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="340969600"/>
+    <pos x="9696450" y="339750400"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5428,7 +5428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="340969600"/>
+    <pos x="11544300" y="339750400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5448,7 +5448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="340969600"/>
+    <pos x="13392150" y="339750400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5468,7 +5468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="342817450"/>
+    <pos x="7848600" y="341598250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5488,7 +5488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="342817450"/>
+    <pos x="9696450" y="341598250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5508,7 +5508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="342817450"/>
+    <pos x="11544300" y="341598250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5528,7 +5528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="356679500"/>
+    <pos x="7848600" y="355460300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5548,7 +5548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="356679500"/>
+    <pos x="9696450" y="355460300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5568,7 +5568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="356679500"/>
+    <pos x="11544300" y="355460300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5588,7 +5588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="356679500"/>
+    <pos x="13392150" y="355460300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5608,7 +5608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="358527350"/>
+    <pos x="7848600" y="357308150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5628,7 +5628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="358527350"/>
+    <pos x="9696450" y="357308150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5648,7 +5648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="358527350"/>
+    <pos x="11544300" y="357308150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5668,7 +5668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="358527350"/>
+    <pos x="13392150" y="357308150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5688,7 +5688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="360375200"/>
+    <pos x="7848600" y="359156000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5708,7 +5708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="360375200"/>
+    <pos x="9696450" y="359156000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5728,7 +5728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="360375200"/>
+    <pos x="11544300" y="359156000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5748,7 +5748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="365683800"/>
+    <pos x="7848600" y="364464600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5768,7 +5768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="365683800"/>
+    <pos x="9696450" y="364464600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5788,7 +5788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="365683800"/>
+    <pos x="11544300" y="364464600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -5808,7 +5808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="365683800"/>
+    <pos x="13392150" y="364464600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5828,7 +5828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="373672100"/>
+    <pos x="7848600" y="372452900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5848,7 +5848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="373672100"/>
+    <pos x="9696450" y="372452900"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -5868,7 +5868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="373672100"/>
+    <pos x="11544300" y="372452900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5888,7 +5888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="373672100"/>
+    <pos x="13392150" y="372452900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5908,7 +5908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="375519950"/>
+    <pos x="7848600" y="374300750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5928,7 +5928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="375519950"/>
+    <pos x="9696450" y="374300750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5948,7 +5948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="375519950"/>
+    <pos x="11544300" y="374300750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5968,7 +5968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="375519950"/>
+    <pos x="13392150" y="374300750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5988,7 +5988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="377367800"/>
+    <pos x="7848600" y="376148600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6008,7 +6008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="377367800"/>
+    <pos x="9696450" y="376148600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6028,7 +6028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="377367800"/>
+    <pos x="11544300" y="376148600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6048,7 +6048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="386130800"/>
+    <pos x="7848600" y="384708400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6068,7 +6068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="386130800"/>
+    <pos x="9696450" y="384708400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6088,7 +6088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="386130800"/>
+    <pos x="11544300" y="384708400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6108,7 +6108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="395135100"/>
+    <pos x="7848600" y="393712700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6128,7 +6128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="407212800"/>
+    <pos x="7848600" y="405790400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6148,7 +6148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="407212800"/>
+    <pos x="9696450" y="405790400"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6168,7 +6168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="407212800"/>
+    <pos x="11544300" y="405790400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6188,7 +6188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="407212800"/>
+    <pos x="13392150" y="405790400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6208,7 +6208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="409060650"/>
+    <pos x="7848600" y="407638250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6228,7 +6228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="409060650"/>
+    <pos x="9696450" y="407638250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6248,7 +6248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="409060650"/>
+    <pos x="11544300" y="407638250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6268,7 +6268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="409060650"/>
+    <pos x="13392150" y="407638250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6288,7 +6288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="418858700"/>
+    <pos x="7848600" y="417436300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6308,7 +6308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="418858700"/>
+    <pos x="9696450" y="417436300"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -6328,7 +6328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="418858700"/>
+    <pos x="11544300" y="417436300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6348,7 +6348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="418858700"/>
+    <pos x="13392150" y="417436300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6368,7 +6368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="420706550"/>
+    <pos x="7848600" y="419284150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6388,7 +6388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="420706550"/>
+    <pos x="9696450" y="419284150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6408,7 +6408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="420706550"/>
+    <pos x="11544300" y="419284150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6428,7 +6428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="420706550"/>
+    <pos x="13392150" y="419284150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6448,7 +6448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="433755800"/>
+    <pos x="7848600" y="432333400"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6468,7 +6468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="439331100"/>
+    <pos x="7848600" y="437908700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6488,7 +6488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="439331100"/>
+    <pos x="9696450" y="437908700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6508,7 +6508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="439331100"/>
+    <pos x="11544300" y="437908700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6528,7 +6528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="439331100"/>
+    <pos x="13392150" y="437908700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6548,7 +6548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="447319400"/>
+    <pos x="7848600" y="445897000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6568,7 +6568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="447319400"/>
+    <pos x="9696450" y="445897000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6588,7 +6588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="447319400"/>
+    <pos x="11544300" y="445897000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6608,7 +6608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="447319400"/>
+    <pos x="13392150" y="445897000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6628,7 +6628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="455104500"/>
+    <pos x="7848600" y="453682100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6648,7 +6648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="455104500"/>
+    <pos x="9696450" y="453682100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6668,7 +6668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="455104500"/>
+    <pos x="11544300" y="453682100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6688,7 +6688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="455104500"/>
+    <pos x="13392150" y="453682100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6708,7 +6708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="456952350"/>
+    <pos x="7848600" y="455529950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6728,7 +6728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="456952350"/>
+    <pos x="9696450" y="455529950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6748,7 +6748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="456952350"/>
+    <pos x="11544300" y="455529950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6768,7 +6768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="464921600"/>
+    <pos x="7848600" y="463499200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6788,7 +6788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="464921600"/>
+    <pos x="9696450" y="463499200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6808,7 +6808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="464921600"/>
+    <pos x="11544300" y="463499200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6828,7 +6828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="464921600"/>
+    <pos x="13392150" y="463499200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6848,7 +6848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="472097100"/>
+    <pos x="7848600" y="470674700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6868,7 +6868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="472097100"/>
+    <pos x="9696450" y="470674700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6888,7 +6888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="472097100"/>
+    <pos x="11544300" y="470674700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6908,7 +6908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="472097100"/>
+    <pos x="13392150" y="470674700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6928,7 +6928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="480085400"/>
+    <pos x="7848600" y="478663000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6948,7 +6948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="480085400"/>
+    <pos x="9696450" y="478663000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6968,7 +6968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="480085400"/>
+    <pos x="11544300" y="478663000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6988,7 +6988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="480085400"/>
+    <pos x="13392150" y="478663000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7008,7 +7008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="481933250"/>
+    <pos x="7848600" y="480510850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7028,7 +7028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="491756700"/>
+    <pos x="7848600" y="490334300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7048,7 +7048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="491756700"/>
+    <pos x="9696450" y="490334300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7068,7 +7068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="491756700"/>
+    <pos x="11544300" y="490334300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7088,7 +7088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="491756700"/>
+    <pos x="13392150" y="490334300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7108,7 +7108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="499541800"/>
+    <pos x="7848600" y="498119400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7128,7 +7128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="499541800"/>
+    <pos x="9696450" y="498119400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7148,7 +7148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="499541800"/>
+    <pos x="11544300" y="498119400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7168,7 +7168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="499541800"/>
+    <pos x="13392150" y="498119400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7188,7 +7188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="509358900"/>
+    <pos x="7848600" y="507936500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7208,7 +7208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="509358900"/>
+    <pos x="9696450" y="507936500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7228,7 +7228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="509358900"/>
+    <pos x="11544300" y="507936500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7248,7 +7248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="509358900"/>
+    <pos x="13392150" y="507936500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7268,7 +7268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="511206750"/>
+    <pos x="7848600" y="509784350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7288,7 +7288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="511206750"/>
+    <pos x="9696450" y="509784350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7308,7 +7308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="511206750"/>
+    <pos x="11544300" y="509784350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7328,7 +7328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="518160000"/>
+    <pos x="7848600" y="516737600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7348,7 +7348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="518160000"/>
+    <pos x="9696450" y="516737600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7368,7 +7368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="518160000"/>
+    <pos x="11544300" y="516737600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7388,7 +7388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="518160000"/>
+    <pos x="13392150" y="516737600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7408,7 +7408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="526351500"/>
+    <pos x="7848600" y="524725900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7428,7 +7428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="526351500"/>
+    <pos x="9696450" y="524725900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7448,7 +7448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="526351500"/>
+    <pos x="11544300" y="524725900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7468,7 +7468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="526351500"/>
+    <pos x="13392150" y="524725900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7488,7 +7488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="532307800"/>
+    <pos x="7848600" y="530682200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7508,7 +7508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="532307800"/>
+    <pos x="9696450" y="530682200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7528,7 +7528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="532307800"/>
+    <pos x="11544300" y="530682200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7548,7 +7548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="532307800"/>
+    <pos x="13392150" y="530682200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7568,7 +7568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="540499300"/>
+    <pos x="7848600" y="538873700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7588,7 +7588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="540499300"/>
+    <pos x="9696450" y="538873700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7608,7 +7608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="540499300"/>
+    <pos x="11544300" y="538873700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7628,7 +7628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="540499300"/>
+    <pos x="13392150" y="538873700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7648,7 +7648,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="542347150"/>
+    <pos x="7848600" y="540721550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7668,7 +7668,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="542347150"/>
+    <pos x="9696450" y="540721550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7688,7 +7688,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="542347150"/>
+    <pos x="11544300" y="540721550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7708,7 +7708,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="542347150"/>
+    <pos x="13392150" y="540721550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7728,7 +7728,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="544195000"/>
+    <pos x="7848600" y="542569400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7748,7 +7748,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="551332400"/>
+    <pos x="7848600" y="549706800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7768,7 +7768,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="551332400"/>
+    <pos x="9696450" y="549706800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7788,7 +7788,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="551332400"/>
+    <pos x="11544300" y="549706800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7808,7 +7808,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="551332400"/>
+    <pos x="13392150" y="549706800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7828,7 +7828,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="553180250"/>
+    <pos x="7848600" y="551554650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7848,7 +7848,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="553180250"/>
+    <pos x="9696450" y="551554650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7868,7 +7868,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="553180250"/>
+    <pos x="11544300" y="551554650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7888,7 +7888,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="553180250"/>
+    <pos x="13392150" y="551554650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7908,7 +7908,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="555028100"/>
+    <pos x="7848600" y="553402500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7928,7 +7928,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="555028100"/>
+    <pos x="9696450" y="553402500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7948,7 +7948,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="564603900"/>
+    <pos x="7848600" y="562978300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7968,7 +7968,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="564603900"/>
+    <pos x="9696450" y="562978300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7988,7 +7988,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="564603900"/>
+    <pos x="11544300" y="562978300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8008,7 +8008,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="564603900"/>
+    <pos x="13392150" y="562978300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8028,7 +8028,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="566451750"/>
+    <pos x="7848600" y="564826150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8048,7 +8048,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="566451750"/>
+    <pos x="9696450" y="564826150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8068,7 +8068,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="566451750"/>
+    <pos x="11544300" y="564826150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8088,7 +8088,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="566451750"/>
+    <pos x="13392150" y="564826150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8108,7 +8108,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="568299600"/>
+    <pos x="7848600" y="566674000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8128,7 +8128,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="568299600"/>
+    <pos x="9696450" y="566674000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8148,7 +8148,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="577062600"/>
+    <pos x="7848600" y="575437000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8168,7 +8168,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="577062600"/>
+    <pos x="9696450" y="575437000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8188,7 +8188,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="577062600"/>
+    <pos x="11544300" y="575437000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8208,7 +8208,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="577062600"/>
+    <pos x="13392150" y="575437000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8228,7 +8228,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="586676500"/>
+    <pos x="7848600" y="585050900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8248,7 +8248,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="586676500"/>
+    <pos x="9696450" y="585050900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8268,7 +8268,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="586676500"/>
+    <pos x="11544300" y="585050900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8288,7 +8288,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="586676500"/>
+    <pos x="13392150" y="585050900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8308,7 +8308,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="588524350"/>
+    <pos x="7848600" y="586898750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8328,7 +8328,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="588524350"/>
+    <pos x="9696450" y="586898750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8348,7 +8348,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="599973400"/>
+    <pos x="7848600" y="598347800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8368,7 +8368,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="599973400"/>
+    <pos x="9696450" y="598347800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8388,7 +8388,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="599973400"/>
+    <pos x="11544300" y="598347800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8408,7 +8408,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="599973400"/>
+    <pos x="13392150" y="598347800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8428,7 +8428,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="609384100"/>
+    <pos x="7848600" y="607758500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8448,7 +8448,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="609384100"/>
+    <pos x="9696450" y="607758500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8468,7 +8468,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="609384100"/>
+    <pos x="11544300" y="607758500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8488,7 +8488,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="609384100"/>
+    <pos x="13392150" y="607758500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8508,7 +8508,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="617575600"/>
+    <pos x="7848600" y="615950000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8528,7 +8528,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="617575600"/>
+    <pos x="9696450" y="615950000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8548,7 +8548,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="617575600"/>
+    <pos x="11544300" y="615950000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8568,7 +8568,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="617575600"/>
+    <pos x="13392150" y="615950000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8588,7 +8588,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="619423450"/>
+    <pos x="7848600" y="617797850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8608,7 +8608,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="619423450"/>
+    <pos x="9696450" y="617797850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8628,7 +8628,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="619423450"/>
+    <pos x="11544300" y="617797850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9073,7 +9073,7 @@
           <t>보습, 턴오버 촉진, 재생, 톤업</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>누룩(천연효모)발효여과물, / 보습, 탄력, / 미네럴 영양 공급</t>
+          <t>누룩(천연효모)발효여과물 · 보습, 탄력 · 미네럴 영양 공급</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>프로바이오틱스3, / 사카로미세스발효여과물</t>
+          <t>프로바이오틱스3 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -9346,12 +9346,12 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>비타민 B3, / 식약처 기능성 고시원료</t>
+          <t>비타민 B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -9533,10 +9533,10 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>커피 활력 핵심원료, / 피부 매끈 탄탄, 끌올</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="n"/>
+          <t>커피 활력 핵심원료 · 피부 매끈 탄탄, 끌올</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>은은한 장미향, 겔타입, / 점증, 진정, 수분</t>
+          <t>은은한 장미향, 겔타입 · 점증, 진정, 수분</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -9753,10 +9753,10 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>주름 개선 기능성 앰플 베이스 / 아데노신, 노니, 인삼, 상황버섯, / 로얄젤리, 동백꽃, 양귀비 , 히비스커스 추출물 등</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="n"/>
+          <t>주름 개선 기능성 앰플 베이스 · 아데노신, 노니, 인삼, 상황버섯 · 로얄젤리, 동백꽃, 양귀비 , 히비스커스 추출물 등</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr"/>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
@@ -9896,16 +9896,16 @@
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>5가지 멀티 세라마이드, / 피부 장벽 강화</t>
+          <t>5가지 멀티 세라마이드 · 피부 장벽 강화</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1">
+          <t>스쿠알란 · 보르피린</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
         <is>
           <t>어린 콜라겐겔</t>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>300Da 초저분자 콜라겐, / 마린 콜라겐 펩타이드 10,000ppm함유</t>
+          <t>300Da 초저분자 콜라겐 · 마린 콜라겐 펩타이드 10,000ppm함유</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산으로 / 피부 속부터 겉까지 수분채움, 단독 사용 가능</t>
+          <t>크기가 다른 11가지 히아루론산으로 · 피부 속부터 겉까지 수분채움, 단독 사용 가능</t>
         </is>
       </c>
       <c r="F49" s="18" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산으로 / 피부 속부터 겉까지 수분채움, 단독 사용 가능</t>
+          <t>크기가 다른 11가지 히아루론산으로 · 피부 속부터 겉까지 수분채움, 단독 사용 가능</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>미백 주름 개선 기능성 / 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
+          <t>미백 주름 개선 기능성 · 나이아신아미이드, 아데노신, 마데카소사이드, 아시아티코사이드, 마데카식애씨드, 아시아틱애씨드, 덱스판테놀 등</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="F75" s="18" t="inlineStr">
         <is>
-          <t>사카로미세스 / 발효여과물, / 원하는 워터</t>
+          <t>사카로미세스 · 발효여과물 · 원하는 워터</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>수입화장품 E사 갈색병의 / 주요성분.</t>
+          <t>수입화장품 E사 갈색병의 · 주요성분.</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>갈락토미세스 / 발효여과물</t>
+          <t>갈락토미세스 · 발효여과물</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>청국장 끈적한 성분,</t>
+          <t>청국장 끈적한 성분</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>유기농 허브 5가지 추출물 / 감초, 올리브잎, 다마스크장미꽃, 바위돌꽃뿌리, 서양민들레,</t>
+          <t>유기농 허브 5가지 추출물 · 감초, 올리브잎, 다마스크장미꽃, 바위돌꽃뿌리, 서양민들레</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>오가닉 7 솔루션 , / 화이텐스 등..</t>
+          <t>오가닉 7 솔루션 · 화이텐스 등..</t>
         </is>
       </c>
     </row>
@@ -10832,12 +10832,12 @@
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>꽃중의 꽃이라는 말레이어. / 일랑일랑 꽃으로 에센셜오일을 (수증기)추출하는 과정에서 / 생기는 부산물, / 피부진정, 피지 균형</t>
+          <t>꽃중의 꽃이라는 말레이어. · 일랑일랑 꽃으로 에센셜오일을 (수증기)추출하는 과정에서 · 생기는 부산물 · 피부진정, 피지 균형</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>수분공급, / 자체점도</t>
+          <t>수분공급 · 자체점도</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>청국장의 끈~적 끈~적한 성분. / 자체보습, / 천연보습인자생성촉진.</t>
+          <t>청국장의 끈~적 끈~적한 성분. · 자체보습 · 천연보습인자생성촉진.</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t>프랑스 세더마사 특허, 볼륨&amp; 탄력 / 핵심원료 지모추출물(지용성), / 힙, 가슴, 이마, 손 등 볼륨을 원하는 곳 / 사용, 추천 용량 5% 내외</t>
+          <t>프랑스 세더마사 특허, 볼륨&amp; 탄력 · 핵심원료 지모추출물(지용성) · 힙, 가슴, 이마, 손 등 볼륨을 원하는 곳 · 사용, 추천 용량 5% 내외</t>
         </is>
       </c>
       <c r="F104" s="18" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>들장미열매를 압착, / 용매 추출,노화,주름피부</t>
+          <t>들장미열매를 압착 · 용매 추출,노화,주름피부</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
+          <t>월견초 종자유 · 감마리놀린산 다량함유</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
           <t>피부보호막, 촉촉함이 오래</t>
         </is>
       </c>
-      <c r="F117" s="10" t="n"/>
+      <c r="F117" s="10" t="inlineStr"/>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="10" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제, / 나트로틱스 / (워터류1g 줄이고 2g)</t>
+          <t>천연한방보존제 · 나트로틱스 · (워터류1g 줄이고 2g)</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
-          <t>상황버섯, 프로폴리스추출물, / 일명 노란만병초라는 복합추출물</t>
+          <t>상황버섯, 프로폴리스추출물 · 일명 노란만병초라는 복합추출물</t>
         </is>
       </c>
       <c r="F131" s="18" t="inlineStr">
@@ -11752,7 +11752,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="32" customHeight="1">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="18" t="inlineStr">
         <is>
           <t>감초추출물</t>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="F132" s="18" t="inlineStr">
         <is>
-          <t>오이, / 녹차추출물</t>
+          <t>오이 · 녹차추출물</t>
         </is>
       </c>
     </row>
@@ -11807,12 +11807,12 @@
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>고보습, / 히아루론산의 2배효과</t>
+          <t>고보습 · 히아루론산의 2배효과</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="E134" s="18" t="inlineStr">
         <is>
-          <t>색소침착억제, / 식약청고시미백성분</t>
+          <t>색소침착억제 · 식약청고시미백성분</t>
         </is>
       </c>
       <c r="F134" s="18" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
-          <t>겔상태, 수분공급, 진정, / 고농축재료들을 희석하는 역할, / 점도증가역할</t>
+          <t>겔상태, 수분공급, 진정 · 고농축재료들을 희석하는 역할 · 점도증가역할</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F136" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>유비퀴논, 비타민 Q 라고 불림. / 심장, 피부 표피에 많은 양, / 20대를 기준으로 줄어듬.</t>
+          <t>유비퀴논, 비타민 Q 라고 불림. · 심장, 피부 표피에 많은 양 · 20대를 기준으로 줄어듬.</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, 미백 승인원료. / 녹황색 채소</t>
+          <t>비타민B3, 미백 승인원료. · 녹황색 채소</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.8g / (코엔자임Q10의 양을 양을 11.6g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.8g · (코엔자임Q10의 양을 양을 11.6g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="96" customHeight="1">
+    <row r="162" ht="80" customHeight="1">
       <c r="A162" s="18" t="inlineStr">
         <is>
           <t>갈락토미세스 / 발효여과물</t>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="E162" s="18" t="inlineStr">
         <is>
-          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. / 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절, / 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
+          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. · 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절 · 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
         </is>
       </c>
       <c r="F162" s="18" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미. / 수증기 증류, 수용성 성분.</t>
+          <t>불가리아 다마스크 장미. · 수증기 증류, 수용성 성분.</t>
         </is>
       </c>
       <c r="F163" s="18" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F164" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 58g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 58g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -12733,10 +12733,10 @@
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>점증제, / 계량스푼 작은 쪽 깍아서 두스푼.</t>
-        </is>
-      </c>
-      <c r="F174" s="10" t="n"/>
+          <t>점증제 · 계량스푼 작은 쪽 깍아서 두스푼.</t>
+        </is>
+      </c>
+      <c r="F174" s="10" t="inlineStr"/>
     </row>
     <row r="175" ht="32" customHeight="1">
       <c r="A175" s="10" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>꿀벌이 만드는 천연항*물질 / 피부면역강화.</t>
+          <t>꿀벌이 만드는 천연항*물질 · 피부면역강화.</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F176" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>상피 재생관여, / 10ppm (또는 1ppm)</t>
+          <t>상피 재생관여 · 10ppm (또는 1ppm)</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>FGF10/1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
+          <t>FGF10 · 1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>진피재생관여, / 10ppm (또는 1ppm)</t>
+          <t>진피재생관여 · 10ppm (또는 1ppm)</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>산초, 백두홍, 이끼추출물 / 식물 복합 균번식 억제제</t>
+          <t>산초, 백두홍, 이끼추출물 · 식물 복합 균번식 억제제</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (꿀추출물의 양을 7.7g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (꿀추출물의 양을 7.7g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>장미 향이 나는 제라늄, / 피지 균형 등 모든 피부</t>
+          <t>장미 향이 나는 제라늄 · 피지 균형 등 모든 피부</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="E189" s="18" t="inlineStr">
         <is>
-          <t>천연 레시틴으로 / 코포아수 버터를 리포좀화</t>
+          <t>천연 레시틴으로 · 코포아수 버터를 리포좀화</t>
         </is>
       </c>
       <c r="F189" s="18" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="F190" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="E192" s="18" t="inlineStr">
         <is>
-          <t>유비퀴논, 비타민 Q 라고 불림, / 심장, 피부 표피에 많은 양, / 20대를 기준으로 줄어듬.</t>
+          <t>유비퀴논, 비타민 Q 라고 불림 · 심장, 피부 표피에 많은 양 · 20대를 기준으로 줄어듬.</t>
         </is>
       </c>
       <c r="F192" s="18" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="F195" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (알로에베라겔의 양을 39g로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (알로에베라겔의 양을 39g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
-          <t>트러블 억제, 손상피부복구, / 생긴 자국으로 남은 색소침착 완화 피부 톤 향상에 도움. / 4가지 복합 펩타이드</t>
+          <t>트러블 억제, 손상피부복구 · 생긴 자국으로 남은 색소침착 완화 피부 톤 향상에 도움. · 4가지 복합 펩타이드</t>
         </is>
       </c>
       <c r="F205" s="10" t="inlineStr">
@@ -13472,10 +13472,10 @@
           <t>활성</t>
         </is>
       </c>
-      <c r="E206" s="10" t="n"/>
+      <c r="E206" s="10" t="inlineStr"/>
       <c r="F206" s="10" t="inlineStr">
         <is>
-          <t>어성초, / 병풀 등</t>
+          <t>어성초 · 병풀 등</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="96" customHeight="1">
+    <row r="218" ht="80" customHeight="1">
       <c r="A218" s="18" t="inlineStr">
         <is>
           <t>갈락토미세스 / 발효여과물</t>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E218" s="18" t="inlineStr">
         <is>
-          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. / 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절, / 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
+          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. · 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절 · 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
         </is>
       </c>
       <c r="F218" s="18" t="inlineStr">
@@ -13773,10 +13773,10 @@
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>24k금가루 / (95%이상, 99.9%) / 피부 정화, 탄탄, / 보습, 피부톤개선</t>
-        </is>
-      </c>
-      <c r="F220" s="18" t="n"/>
+          <t>24k금가루 · (95%이상, 99.9%) · 피부 정화, 탄탄 · 보습, 피부톤개선</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr"/>
     </row>
     <row r="221" ht="80" customHeight="1">
       <c r="A221" s="18" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F223" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13897,7 +13897,7 @@
       </c>
       <c r="E224" s="18" t="inlineStr">
         <is>
-          <t>선택가능원료. / 비타민나무 열매오일, / 갈색을 띈 오렌지색.</t>
+          <t>선택가능원료. · 비타민나무 열매오일 · 갈색을 띈 오렌지색.</t>
         </is>
       </c>
       <c r="F224" s="18" t="inlineStr">
@@ -14098,7 +14098,7 @@
         </is>
       </c>
     </row>
-    <row r="235" ht="96" customHeight="1">
+    <row r="235" ht="80" customHeight="1">
       <c r="A235" s="10" t="inlineStr">
         <is>
           <t>갈락토미세스 / 발효여과물</t>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="E235" s="10" t="inlineStr">
         <is>
-          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. / 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절, / 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
+          <t>술을 빚을 때 사용하는 누룩을 발효시켜 얻음. · 피부에 아미노산과 미네럴 등 풍부한 영양을 공급, 유수분 조절 · 피부장벽강화 및 칙칙한 피부 톤을 개선</t>
         </is>
       </c>
       <c r="F235" s="10" t="inlineStr">
@@ -14153,10 +14153,10 @@
       </c>
       <c r="E236" s="10" t="inlineStr">
         <is>
-          <t>24k금가루 / (95%이상, 99.9%) / 피부 정화, 탄탄, / 보습, 피부톤개선</t>
-        </is>
-      </c>
-      <c r="F236" s="10" t="n"/>
+          <t>24k금가루 · (95%이상, 99.9%) · 피부 정화, 탄탄 · 보습, 피부톤개선</t>
+        </is>
+      </c>
+      <c r="F236" s="10" t="inlineStr"/>
     </row>
     <row r="237" ht="32" customHeight="1">
       <c r="A237" s="10" t="inlineStr">
@@ -14181,10 +14181,10 @@
       </c>
       <c r="E237" s="10" t="inlineStr">
         <is>
-          <t>기능성 미백, 보습, / 수분크림베이스</t>
-        </is>
-      </c>
-      <c r="F237" s="10" t="n"/>
+          <t>기능성 미백, 보습 · 수분크림베이스</t>
+        </is>
+      </c>
+      <c r="F237" s="10" t="inlineStr"/>
     </row>
     <row r="238" ht="96" customHeight="1">
       <c r="A238" s="10" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="E239" s="10" t="inlineStr">
         <is>
-          <t>비타민 나무, / 진한 오렌지색</t>
+          <t>비타민 나무 · 진한 오렌지색</t>
         </is>
       </c>
       <c r="F239" s="10" t="inlineStr">
         <is>
-          <t>코엔자임Q10 / (수용성)</t>
+          <t>코엔자임Q10 · (수용성)</t>
         </is>
       </c>
     </row>
@@ -14437,10 +14437,10 @@
       </c>
       <c r="E250" s="18" t="inlineStr">
         <is>
-          <t>피부정화, 보습, / 피부탄탄, 피부 톤보정</t>
-        </is>
-      </c>
-      <c r="F250" s="18" t="n"/>
+          <t>피부정화, 보습 · 피부탄탄, 피부 톤보정</t>
+        </is>
+      </c>
+      <c r="F250" s="18" t="inlineStr"/>
     </row>
     <row r="251" ht="32" customHeight="1">
       <c r="A251" s="18" t="inlineStr">
@@ -14465,10 +14465,10 @@
       </c>
       <c r="E251" s="18" t="inlineStr">
         <is>
-          <t>미백 기능성, 보습 / 아르간가득한 크림베이스</t>
-        </is>
-      </c>
-      <c r="F251" s="18" t="n"/>
+          <t>미백 기능성, 보습 · 아르간가득한 크림베이스</t>
+        </is>
+      </c>
+      <c r="F251" s="18" t="inlineStr"/>
     </row>
     <row r="252" ht="32" customHeight="1">
       <c r="A252" s="18" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="E252" s="18" t="inlineStr">
         <is>
-          <t>오렌지꽃오일, / 민감,탄력을 잃은 피부</t>
+          <t>오렌지꽃오일 · 민감,탄력을 잃은 피부</t>
         </is>
       </c>
       <c r="F252" s="18" t="inlineStr">
@@ -14525,12 +14525,12 @@
       </c>
       <c r="E253" s="18" t="inlineStr">
         <is>
-          <t>비타민 나무, / 진한 오렌지색</t>
+          <t>비타민 나무 · 진한 오렌지색</t>
         </is>
       </c>
       <c r="F253" s="18" t="inlineStr">
         <is>
-          <t>코엔자임Q10 / (수용성)</t>
+          <t>코엔자임Q10 · (수용성)</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
           <t>사탕수수에서 채취한 점증제</t>
         </is>
       </c>
-      <c r="F263" s="10" t="n"/>
+      <c r="F263" s="10" t="inlineStr"/>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="10" t="inlineStr">
@@ -14759,12 +14759,12 @@
       </c>
       <c r="E265" s="10" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 4가지 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 4가지 펩타이드</t>
         </is>
       </c>
       <c r="F265" s="10" t="inlineStr">
         <is>
-          <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
+          <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="E266" s="10" t="inlineStr">
         <is>
-          <t>청국장의 끈적한 성분 , / 천연보습제, 감마 PGA불림.</t>
+          <t>청국장의 끈적한 성분 · 천연보습제, 감마 PGA불림.</t>
         </is>
       </c>
       <c r="F266" s="10" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="E267" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 인증 미백원료</t>
+          <t>비타민B3 · 식약처 인증 미백원료</t>
         </is>
       </c>
       <c r="F267" s="10" t="inlineStr">
@@ -14855,10 +14855,10 @@
       </c>
       <c r="E268" s="10" t="inlineStr">
         <is>
-          <t>베트남산 해초, / 포도같아 바다포도, / 풍부한 미네럴, / 후코이단 함유</t>
-        </is>
-      </c>
-      <c r="F268" s="10" t="n"/>
+          <t>베트남산 해초 · 포도같아 바다포도 · 풍부한 미네럴 · 후코이단 함유</t>
+        </is>
+      </c>
+      <c r="F268" s="10" t="inlineStr"/>
     </row>
     <row r="269" ht="64" customHeight="1">
       <c r="A269" s="10" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="F269" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올1g / (네롤리워터의 양을 24.5g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올1g · (네롤리워터의 양을 24.5g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="E278" s="18" t="inlineStr">
         <is>
-          <t>불가리아 장미수, / 은은한 천연 장미향</t>
+          <t>불가리아 장미수 · 은은한 천연 장미향</t>
         </is>
       </c>
       <c r="F278" s="18" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="F279" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -15117,12 +15117,12 @@
       </c>
       <c r="E281" s="18" t="inlineStr">
         <is>
-          <t>아세틸헥사펩타이드-8, / 농도 500ppm</t>
+          <t>아세틸헥사펩타이드-8 · 농도 500ppm</t>
         </is>
       </c>
       <c r="F281" s="18" t="inlineStr">
         <is>
-          <t>아데노신, / EGF등</t>
+          <t>아데노신 · EGF등</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="F282" s="18" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="F283" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올1g / (로즈워터의 양을 19.5g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올1g · (로즈워터의 양을 19.5g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15337,10 +15337,10 @@
       </c>
       <c r="E292" s="10" t="inlineStr">
         <is>
-          <t>30%, 3000ppm / 코엔자임 Q10의 10배 항산화, / 리포좀</t>
-        </is>
-      </c>
-      <c r="F292" s="10" t="n"/>
+          <t>30%, 3000ppm · 코엔자임 Q10의 10배 항산화 · 리포좀</t>
+        </is>
+      </c>
+      <c r="F292" s="10" t="inlineStr"/>
     </row>
     <row r="293" ht="32" customHeight="1">
       <c r="A293" s="10" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="F295" s="10" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="F296" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.8g / (히아루론산의 양을23.6g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.8g · (히아루론산의 양을23.6g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="E297" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 버가못FCF, 일랑일랑, / 프랑킨센스에센셜오일 복합브랜딩</t>
+          <t>네롤리, 버가못FCF, 일랑일랑 · 프랑킨센스에센셜오일 복합브랜딩</t>
         </is>
       </c>
       <c r="F297" s="10" t="inlineStr">
@@ -15666,7 +15666,7 @@
           <t>사탕수수 채취, 점증제</t>
         </is>
       </c>
-      <c r="F307" s="18" t="n"/>
+      <c r="F307" s="18" t="inlineStr"/>
     </row>
     <row r="308" ht="32" customHeight="1">
       <c r="A308" s="18" t="inlineStr">
@@ -15691,10 +15691,10 @@
       </c>
       <c r="E308" s="18" t="inlineStr">
         <is>
-          <t>완성시 2000ppm / 코엔자임의 10배의 항산화효과, 황금톡스</t>
-        </is>
-      </c>
-      <c r="F308" s="18" t="n"/>
+          <t>완성시 2000ppm · 코엔자임의 10배의 항산화효과, 황금톡스</t>
+        </is>
+      </c>
+      <c r="F308" s="18" t="inlineStr"/>
     </row>
     <row r="309" ht="16" customHeight="1">
       <c r="A309" s="18" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F313" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.8g / (네롤리워터의 양을 17.1g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.8g · (네롤리워터의 양을 17.1g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="F323" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -16060,12 +16060,12 @@
       </c>
       <c r="E324" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수를 듬뿍 담은겔, / 에코보습제, 알란토인 함유</t>
+          <t>불가리아 다마스크 장미수를 듬뿍 담은겔 · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
       <c r="F324" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="E325" s="10" t="inlineStr">
         <is>
-          <t>테트라펩타이드-44, 쿠퍼펩타이드-1, / 헥사펩타이드-9, 화이트펩타이드-23로 / 구성된 4가지 복합 펩타이드,1000ppm, / 트러블관리에 도움</t>
+          <t>테트라펩타이드-44, 쿠퍼펩타이드-1 · 헥사펩타이드-9, 화이트펩타이드-23로 · 구성된 4가지 복합 펩타이드,1000ppm · 트러블관리에 도움</t>
         </is>
       </c>
       <c r="F325" s="10" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="F326" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈마리워터의 양을 39g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈마리워터의 양을 39g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16156,7 @@
       </c>
       <c r="E327" s="10" t="inlineStr">
         <is>
-          <t>티트리, 버가못FCF, 라벤더EO가 / 블렌딩된 오일</t>
+          <t>티트리, 버가못FCF, 라벤더EO가 · 블렌딩된 오일</t>
         </is>
       </c>
       <c r="F327" s="10" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="E336" s="18" t="inlineStr">
         <is>
-          <t>누룩(천연효모)발효여과물, / 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
+          <t>누룩(천연효모)발효여과물 · 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
         </is>
       </c>
       <c r="F336" s="18" t="inlineStr">
         <is>
-          <t>사카로미세스 / 발효여과물</t>
+          <t>사카로미세스 · 발효여과물</t>
         </is>
       </c>
     </row>
@@ -16357,10 +16357,10 @@
       </c>
       <c r="E338" s="18" t="inlineStr">
         <is>
-          <t>완성시1000ppm. / 코엔자임의 10배,항산화효과</t>
-        </is>
-      </c>
-      <c r="F338" s="18" t="n"/>
+          <t>완성시1000ppm. · 코엔자임의 10배,항산화효과</t>
+        </is>
+      </c>
+      <c r="F338" s="18" t="inlineStr"/>
     </row>
     <row r="339" ht="64" customHeight="1">
       <c r="A339" s="18" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="E339" s="18" t="inlineStr">
         <is>
-          <t>고분자+중분자+저분자, 보습. / 피부타입에 맞게 / 조절하세요. / ※많은양 첨가할 경우 물총처럼 분사됨</t>
+          <t>고분자+중분자+저분자, 보습. · 피부타입에 맞게 · 조절하세요. · ※많은양 첨가할 경우 물총처럼 분사됨</t>
         </is>
       </c>
       <c r="F339" s="18" t="inlineStr">
@@ -16603,12 +16603,12 @@
       </c>
       <c r="E350" s="10" t="inlineStr">
         <is>
-          <t>누룩(천연효모)발효여과물, / 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
+          <t>누룩(천연효모)발효여과물 · 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
         </is>
       </c>
       <c r="F350" s="10" t="inlineStr">
         <is>
-          <t>사카로미세스 / 발효여과물, / 원하는 워터</t>
+          <t>사카로미세스 · 발효여과물 · 원하는 워터</t>
         </is>
       </c>
     </row>
@@ -16667,10 +16667,10 @@
       </c>
       <c r="E352" s="10" t="inlineStr">
         <is>
-          <t>완성시500ppm. / 코엔자임의 10배,항산화효과</t>
-        </is>
-      </c>
-      <c r="F352" s="10" t="n"/>
+          <t>완성시500ppm. · 코엔자임의 10배,항산화효과</t>
+        </is>
+      </c>
+      <c r="F352" s="10" t="inlineStr"/>
     </row>
     <row r="353" ht="64" customHeight="1">
       <c r="A353" s="10" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="E362" s="18" t="inlineStr">
         <is>
-          <t>사람피지와 비슷한 구조, 액상왁스, 가벼운 흡수력, 피부장벽강화 / 비중이 0.86, 3.5ml 피부타입에 따라 1~2g 추가 가능.</t>
+          <t>사람피지와 비슷한 구조, 액상왁스, 가벼운 흡수력, 피부장벽강화 · 비중이 0.86, 3.5ml 피부타입에 따라 1~2g 추가 가능.</t>
         </is>
       </c>
       <c r="F362" s="18" t="inlineStr">
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E363" s="18" t="inlineStr">
         <is>
-          <t>불가리아 로즈워터, pH5내외 / 피부 진정, 보습</t>
+          <t>불가리아 로즈워터, pH5내외 · 피부 진정, 보습</t>
         </is>
       </c>
       <c r="F363" s="18" t="inlineStr">
         <is>
-          <t>네롤리워터 / 또는 / 식염수</t>
+          <t>네롤리워터 · 또는 · 식염수</t>
         </is>
       </c>
     </row>
@@ -17093,12 +17093,12 @@
       </c>
       <c r="E374" s="10" t="inlineStr">
         <is>
-          <t>피부 겉과 속을 재생에 도움을 주는 / 4가지 성장인자</t>
+          <t>피부 겉과 속을 재생에 도움을 주는 · 4가지 성장인자</t>
         </is>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
-          <t>피부타입에 따라 / 다양한 기능성원료</t>
+          <t>피부타입에 따라 · 다양한 기능성원료</t>
         </is>
       </c>
     </row>
@@ -17272,12 +17272,12 @@
       </c>
       <c r="E384" s="18" t="inlineStr">
         <is>
-          <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
+          <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
       <c r="F384" s="18" t="inlineStr">
         <is>
-          <t>아카시아, / 마린콜라겐</t>
+          <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
@@ -17304,12 +17304,12 @@
       </c>
       <c r="E385" s="18" t="inlineStr">
         <is>
-          <t>비타민B2, B3, C, 섬유질 및 / 각종 아미노산 풍부 / 항산화, 화이트닝</t>
+          <t>비타민B2, B3, C, 섬유질 및 · 각종 아미노산 풍부 · 항산화, 화이트닝</t>
         </is>
       </c>
       <c r="F385" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="E386" s="18" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 고시 미백원료</t>
+          <t>비타민B3 · 식약처 고시 미백원료</t>
         </is>
       </c>
       <c r="F386" s="18" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="F387" s="18" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, / 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀 · 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="F388" s="18" t="inlineStr">
         <is>
-          <t>히아루론산. / 글리세린</t>
+          <t>히아루론산. · 글리세린</t>
         </is>
       </c>
     </row>
@@ -17432,12 +17432,12 @@
       </c>
       <c r="E389" s="18" t="inlineStr">
         <is>
-          <t>폴리페놀, 타닌, 라니롤, / 리모넨등 다량 풍부, 피부진정</t>
+          <t>폴리페놀, 타닌, 라니롤 · 리모넨등 다량 풍부, 피부진정</t>
         </is>
       </c>
       <c r="F389" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -17464,12 +17464,12 @@
       </c>
       <c r="E390" s="18" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F390" s="18" t="inlineStr">
         <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워젤</t>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="F391" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -17712,10 +17712,10 @@
       </c>
       <c r="E402" s="10" t="inlineStr">
         <is>
-          <t>24k금가루 / (95%이상, 99.9%) / 피부 정화, 탄탄, / 보습, 피부톤개선</t>
-        </is>
-      </c>
-      <c r="F402" s="10" t="n"/>
+          <t>24k금가루 · (95%이상, 99.9%) · 피부 정화, 탄탄 · 보습, 피부톤개선</t>
+        </is>
+      </c>
+      <c r="F402" s="10" t="inlineStr"/>
     </row>
     <row r="403" ht="32" customHeight="1">
       <c r="A403" s="10" t="inlineStr">
@@ -17743,7 +17743,7 @@
           <t>코엔자임의 10배의 항산화효과, 황금톡스</t>
         </is>
       </c>
-      <c r="F403" s="10" t="n"/>
+      <c r="F403" s="10" t="inlineStr"/>
     </row>
     <row r="404" ht="48" customHeight="1">
       <c r="A404" s="10" t="inlineStr">
@@ -17768,12 +17768,12 @@
       </c>
       <c r="E404" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수를 듬뿍 담은젤, / 에코보습제, / 알란토인 함유</t>
+          <t>불가리아 다마스크 장미수를 듬뿍 담은젤 · 에코보습제 · 알란토인 함유</t>
         </is>
       </c>
       <c r="F404" s="10" t="inlineStr">
         <is>
-          <t>네롤리플라워겔, / 알로에베라겔</t>
+          <t>네롤리플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E405" s="10" t="inlineStr">
         <is>
-          <t>'바르는 보톡스' 등으로 인기, 2~4% 사용. / 독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. / 4%함유 제품을 하루에 두번, 28일간 사용 임상시 / 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득.</t>
+          <t>'바르는 보톡스' 등으로 인기, 2~4% 사용. · 독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. · 4%함유 제품을 하루에 두번, 28일간 사용 임상시 · 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득.</t>
         </is>
       </c>
       <c r="F405" s="10" t="inlineStr">
         <is>
-          <t>아데노신, / EGF등</t>
+          <t>아데노신 · EGF등</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="E406" s="10" t="inlineStr">
         <is>
-          <t>보습제, 자유수 억제, / 균번식억제</t>
+          <t>보습제, 자유수 억제 · 균번식억제</t>
         </is>
       </c>
       <c r="F406" s="10" t="inlineStr">
@@ -17977,7 +17977,7 @@
       </c>
       <c r="F415" s="18" t="inlineStr">
         <is>
-          <t>슈퍼 곡물 / 단백질추출물</t>
+          <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E416" s="18" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F416" s="18" t="inlineStr">
@@ -18068,10 +18068,10 @@
       </c>
       <c r="E418" s="18" t="inlineStr">
         <is>
-          <t>로즈마리, 캐모마일, 녹차, / 병풀, 감초, 호장근, 황금 / 복합추출물</t>
-        </is>
-      </c>
-      <c r="F418" s="18" t="n"/>
+          <t>로즈마리, 캐모마일, 녹차 · 병풀, 감초, 호장근, 황금 · 복합추출물</t>
+        </is>
+      </c>
+      <c r="F418" s="18" t="inlineStr"/>
     </row>
     <row r="419" ht="32" customHeight="1">
       <c r="A419" s="18" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="E419" s="18" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 고시 미백원료</t>
+          <t>비타민B3 · 식약처 고시 미백원료</t>
         </is>
       </c>
       <c r="F419" s="18" t="inlineStr">
@@ -18128,12 +18128,12 @@
       </c>
       <c r="E420" s="18" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF 함유. / 속과 겉 관리</t>
+          <t>EGF, FGF, IGF, TGF 함유. · 속과 겉 관리</t>
         </is>
       </c>
       <c r="F420" s="18" t="inlineStr">
         <is>
-          <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
+          <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="F421" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="E430" s="10" t="inlineStr">
         <is>
-          <t>고중저분자, / 트리플 히아루론산</t>
+          <t>고중저분자 · 트리플 히아루론산</t>
         </is>
       </c>
       <c r="F430" s="10" t="inlineStr">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="F431" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="E432" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F432" s="10" t="inlineStr">
@@ -18409,10 +18409,10 @@
       </c>
       <c r="E433" s="10" t="inlineStr">
         <is>
-          <t>로즈마리, 캐모마일, 녹차, / 병풀, 감초, 호장근, 황금 / 복합추출물</t>
-        </is>
-      </c>
-      <c r="F433" s="10" t="n"/>
+          <t>로즈마리, 캐모마일, 녹차 · 병풀, 감초, 호장근, 황금 · 복합추출물</t>
+        </is>
+      </c>
+      <c r="F433" s="10" t="inlineStr"/>
     </row>
     <row r="434" ht="16" customHeight="1">
       <c r="A434" s="10" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="E435" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F435" s="10" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="E436" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 고시 미백원료</t>
+          <t>비타민B3 · 식약처 고시 미백원료</t>
         </is>
       </c>
       <c r="F436" s="10" t="inlineStr">
@@ -18648,7 +18648,7 @@
         </is>
       </c>
     </row>
-    <row r="446" ht="128" customHeight="1">
+    <row r="446" ht="112" customHeight="1">
       <c r="A446" s="18" t="inlineStr">
         <is>
           <t>AC클리어앰플</t>
@@ -18671,10 +18671,10 @@
       </c>
       <c r="E446" s="18" t="inlineStr">
         <is>
-          <t>프로폴리스, 황금추출물, 호장근추출물, 어성초추출물, 알란토인, 마데카소사이드, 캐모마일추출물, 병풀추출물(센텔라아시아티카), 녹차추출물, / 로즈마리잎추출물 등 피부 진정과 회복에 / 탁월한 성분을 최적의 배합</t>
-        </is>
-      </c>
-      <c r="F446" s="18" t="n"/>
+          <t>프로폴리스, 황금추출물, 호장근추출물, 어성초추출물, 알란토인, 마데카소사이드, 캐모마일추출물, 병풀추출물(센텔라아시아티카), 녹차추출물 · 로즈마리잎추출물 등 피부 진정과 회복에 · 탁월한 성분을 최적의 배합</t>
+        </is>
+      </c>
+      <c r="F446" s="18" t="inlineStr"/>
     </row>
     <row r="447" ht="64" customHeight="1">
       <c r="A447" s="18" t="inlineStr">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="E447" s="18" t="inlineStr">
         <is>
-          <t>병풀의 핵심성분 4가지 복합물 / Madecassoside, Asiaticoside, Asiatic Acid, Madecassic Acid</t>
+          <t>병풀의 핵심성분 4가지 복합물 · Madecassoside, Asiaticoside, Asiatic Acid, Madecassic Acid</t>
         </is>
       </c>
       <c r="F447" s="18" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="E456" s="10" t="inlineStr">
         <is>
-          <t>고중저분자, / 트리플 히아루론산</t>
+          <t>고중저분자 · 트리플 히아루론산</t>
         </is>
       </c>
       <c r="F456" s="10" t="inlineStr">
@@ -18925,10 +18925,10 @@
       </c>
       <c r="E458" s="10" t="inlineStr">
         <is>
-          <t>피부 생기를 위해 엄선한 / 11가지 비타민 컴플렉스</t>
-        </is>
-      </c>
-      <c r="F458" s="10" t="n"/>
+          <t>피부 생기를 위해 엄선한 · 11가지 비타민 컴플렉스</t>
+        </is>
+      </c>
+      <c r="F458" s="10" t="inlineStr"/>
     </row>
     <row r="459" ht="48" customHeight="1">
       <c r="A459" s="10" t="inlineStr">
@@ -18953,12 +18953,12 @@
       </c>
       <c r="E459" s="10" t="inlineStr">
         <is>
-          <t>로즈마리, 캐모마일, 녹차, / 병풀, 감초, 호장근, 황금 / 복합추출물</t>
+          <t>로즈마리, 캐모마일, 녹차 · 병풀, 감초, 호장근, 황금 · 복합추출물</t>
         </is>
       </c>
       <c r="F459" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="E461" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F461" s="10" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="E462" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 고시 미백원료</t>
+          <t>비타민B3 · 식약처 고시 미백원료</t>
         </is>
       </c>
       <c r="F462" s="10" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="F463" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g, / (네롤리워터를 26g으로 늘려주세요)</t>
+          <t>천연한방보존제1g · (네롤리워터를 26g으로 늘려주세요)</t>
         </is>
       </c>
     </row>
@@ -19211,10 +19211,10 @@
       </c>
       <c r="E472" s="18" t="inlineStr">
         <is>
-          <t>코코넛 유래, / 가볍고 빠른 흡수력</t>
-        </is>
-      </c>
-      <c r="F472" s="18" t="n"/>
+          <t>코코넛 유래 · 가볍고 빠른 흡수력</t>
+        </is>
+      </c>
+      <c r="F472" s="18" t="inlineStr"/>
     </row>
     <row r="473" ht="32" customHeight="1">
       <c r="A473" s="18" t="inlineStr">
@@ -19244,7 +19244,7 @@
       </c>
       <c r="F473" s="18" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="E474" s="18" t="inlineStr">
         <is>
-          <t>실크아미노산+마린엘라스틴 / 모발 윤기</t>
+          <t>실크아미노산+마린엘라스틴 · 모발 윤기</t>
         </is>
       </c>
       <c r="F474" s="18" t="inlineStr">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="E475" s="18" t="inlineStr">
         <is>
-          <t>단백질 케어로 / 모발과 두피를 더 건강하게</t>
+          <t>단백질 케어로 · 모발과 두피를 더 건강하게</t>
         </is>
       </c>
       <c r="F475" s="18" t="inlineStr">
@@ -19338,7 +19338,7 @@
           <t>모발성장, 보습</t>
         </is>
       </c>
-      <c r="F476" s="18" t="n"/>
+      <c r="F476" s="18" t="inlineStr"/>
     </row>
     <row r="477" ht="64" customHeight="1">
       <c r="A477" s="18" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="F477" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
           <t>연마 작용</t>
         </is>
       </c>
-      <c r="F487" s="10" t="n"/>
+      <c r="F487" s="10" t="inlineStr"/>
     </row>
     <row r="488" ht="32" customHeight="1">
       <c r="A488" s="10" t="inlineStr">
@@ -19581,10 +19581,10 @@
       </c>
       <c r="E488" s="10" t="inlineStr">
         <is>
-          <t>균형을 유지해주는 약알카리성분, / 탈취, 중화, 발포</t>
-        </is>
-      </c>
-      <c r="F488" s="10" t="n"/>
+          <t>균형을 유지해주는 약알카리성분 · 탈취, 중화, 발포</t>
+        </is>
+      </c>
+      <c r="F488" s="10" t="inlineStr"/>
     </row>
     <row r="489" ht="32" customHeight="1">
       <c r="A489" s="10" t="inlineStr">
@@ -19609,10 +19609,10 @@
       </c>
       <c r="E489" s="10" t="inlineStr">
         <is>
-          <t>단맛과 청량감을 부여, / 구강 세균의 산 생성 감소</t>
-        </is>
-      </c>
-      <c r="F489" s="10" t="n"/>
+          <t>단맛과 청량감을 부여 · 구강 세균의 산 생성 감소</t>
+        </is>
+      </c>
+      <c r="F489" s="10" t="inlineStr"/>
     </row>
     <row r="490" ht="32" customHeight="1">
       <c r="A490" s="10" t="inlineStr">
@@ -19640,7 +19640,7 @@
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F490" s="10" t="n"/>
+      <c r="F490" s="10" t="inlineStr"/>
     </row>
     <row r="491" ht="96" customHeight="1">
       <c r="A491" s="10" t="inlineStr">
@@ -19665,12 +19665,12 @@
       </c>
       <c r="E491" s="10" t="inlineStr">
         <is>
-          <t>가루 원료들을 서로 잘 뭉치게 해 / 고체 형태를 유지</t>
+          <t>가루 원료들을 서로 잘 뭉치게 해 · 고체 형태를 유지</t>
         </is>
       </c>
       <c r="F491" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="F504" s="18" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -19994,12 +19994,12 @@
       </c>
       <c r="E506" s="18" t="inlineStr">
         <is>
-          <t>고보습, 사람의 세포막을 만드는 단백질의 일종, 합성재료이지만 생체친화성이 있는 안전성이 높은 성분으로 체내에 매식하는 인공혈관/세포막 등의 의료분야에서 사용.</t>
+          <t>고보습, 사람의 세포막을 만드는 단백질의 일종, 합성재료이지만 생체친화성이 있는 안전성이 높은 성분으로 체내에 매식하는 인공혈관 · 세포막 등의 의료분야에서 사용.</t>
         </is>
       </c>
       <c r="F506" s="18" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F518" s="10" t="n"/>
+      <c r="F518" s="10" t="inlineStr"/>
     </row>
     <row r="519" ht="32" customHeight="1">
       <c r="A519" s="10" t="inlineStr">
@@ -20304,12 +20304,12 @@
       </c>
       <c r="E520" s="10" t="inlineStr">
         <is>
-          <t>석류의 지/수용성 유효성분을 추출</t>
+          <t>석류의 지 · 수용성 유효성분을 추출</t>
         </is>
       </c>
       <c r="F520" s="10" t="inlineStr">
         <is>
-          <t>콜라겐, 플라센타, / 인삼추출물 등...</t>
+          <t>콜라겐, 플라센타 · 인삼추출물 등...</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="F535" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20836,7 @@
       </c>
       <c r="F545" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="E547" s="10" t="inlineStr">
         <is>
-          <t>한방 추출물 국화산 / (감국, 만형자, 측백엽, 천궁, 백지, 세신, 상백피, 한련초) / + / Mexico 고산지대 천연 식물추출물 / (호호바, 에스피노질리아, 호두, 아보카도, 알로에, 카모마일, 네틀, 엘더베리) / 혼합추출물입니다.</t>
+          <t>한방 추출물 국화산 · (감국, 만형자, 측백엽, 천궁, 백지, 세신, 상백피, 한련초) · + · Mexico 고산지대 천연 식물추출물 · (호호바, 에스피노질리아, 호두, 아보카도, 알로에, 카모마일, 네틀, 엘더베리) · 혼합추출물입니다.</t>
         </is>
       </c>
       <c r="F547" s="10" t="inlineStr">
@@ -20927,12 +20927,12 @@
       </c>
       <c r="E548" s="10" t="inlineStr">
         <is>
-          <t>오배자, 가자, 석곡, 산초를 초음파 방식으로 추출하여 조합한 / 화장품용 천연유래 항균제.</t>
+          <t>오배자, 가자, 석곡, 산초를 초음파 방식으로 추출하여 조합한 · 화장품용 천연유래 항균제.</t>
         </is>
       </c>
       <c r="F548" s="10" t="inlineStr">
         <is>
-          <t>수용성 / 보존제</t>
+          <t>수용성 · 보존제</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F558" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E559" s="18" t="inlineStr">
         <is>
-          <t>'꽃중의 꽃'이라는 꽃말, 목련과허브, / 일랑일랑 꽃을 수증기추출법, 수분공급, 모든 피부</t>
+          <t>'꽃중의 꽃'이라는 꽃말, 목련과허브 · 일랑일랑 꽃을 수증기추출법, 수분공급, 모든 피부</t>
         </is>
       </c>
       <c r="F559" s="18" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="F560" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E561" s="18" t="inlineStr">
         <is>
-          <t>녹황색채소유래, 비타민B3. 분말타입, 트러브, 화이트, 노화, 피부장벽강화 4가지가 하나로, 식약청 기능성승인원료,</t>
+          <t>녹황색채소유래, 비타민B3. 분말타입, 트러브, 화이트, 노화, 피부장벽강화 4가지가 하나로, 식약청 기능성승인원료</t>
         </is>
       </c>
       <c r="F561" s="18" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="F562" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (일랑일랑워터의 양을 37g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (일랑일랑워터의 양을 37g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="E572" s="10" t="inlineStr">
         <is>
-          <t>술을 빚을 때 사용하는 누룩(천연효모)을 발효시켜 얻은 / 100%갈락토미세스발효여과물은... / 피부에 아미노산과 미네럴 등 풍부한 영양을 공급하여 유수분 조절, / 탄력강화 피부 결 및 칙칙한 피부 톤을 개선하여 맑고 투명한 촉촉한 피부로 만들어 줍니다.</t>
+          <t>술을 빚을 때 사용하는 누룩(천연효모)을 발효시켜 얻은 · 100%갈락토미세스발효여과물은... · 피부에 아미노산과 미네럴 등 풍부한 영양을 공급하여 유수분 조절 · 탄력강화 피부 결 및 칙칙한 피부 톤을 개선하여 맑고 투명한 촉촉한 피부로 만들어 줍니다.</t>
         </is>
       </c>
       <c r="F572" s="10" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="E582" s="18" t="inlineStr">
         <is>
-          <t>비타민성분 함유, / 영양공급, 보습</t>
+          <t>비타민성분 함유 · 영양공급, 보습</t>
         </is>
       </c>
       <c r="F582" s="18" t="inlineStr">
@@ -21642,16 +21642,16 @@
       </c>
       <c r="E583" s="18" t="inlineStr">
         <is>
-          <t>에코인증. 올리브오일에서 유래, / 오일과 물이 분리저지</t>
+          <t>에코인증. 올리브오일에서 유래 · 오일과 물이 분리저지</t>
         </is>
       </c>
       <c r="F583" s="18" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="584" ht="48" customHeight="1">
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="32" customHeight="1">
       <c r="A584" s="18" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
@@ -21674,7 +21674,7 @@
       </c>
       <c r="E584" s="18" t="inlineStr">
         <is>
-          <t>에코인증, 올리브유화왁스 보조, / 백탁현상 줄이고 유화 안정.</t>
+          <t>에코인증, 올리브유화왁스 보조 · 백탁현상 줄이고 유화 안정.</t>
         </is>
       </c>
       <c r="F584" s="18" t="inlineStr">
@@ -21706,12 +21706,12 @@
       </c>
       <c r="E585" s="18" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F585" s="18" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="F586" s="18" t="inlineStr">
         <is>
-          <t>에코보습제, / 리피듀어, / 식물성글리세린</t>
+          <t>에코보습제 · 리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="F587" s="18" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -21802,12 +21802,12 @@
       </c>
       <c r="E588" s="18" t="inlineStr">
         <is>
-          <t>진정, 수딩, / 자체 점증, 유화 안정.</t>
+          <t>진정, 수딩 · 자체 점증, 유화 안정.</t>
         </is>
       </c>
       <c r="F588" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="F589" s="18" t="inlineStr">
         <is>
-          <t>코엔자임Q10(수용성), / EGF</t>
+          <t>코엔자임Q10(수용성) · EGF</t>
         </is>
       </c>
     </row>
@@ -21866,12 +21866,12 @@
       </c>
       <c r="E590" s="18" t="inlineStr">
         <is>
-          <t>천연유래 복합, / 균번식 억제제</t>
+          <t>천연유래 복합 · 균번식 억제제</t>
         </is>
       </c>
       <c r="F590" s="18" t="inlineStr">
         <is>
-          <t>수용성보존제, / 나트로틱스2g / (정제수51g으로 변경)</t>
+          <t>수용성보존제 · 나트로틱스2g · (정제수51g으로 변경)</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22064,7 @@
       </c>
       <c r="F600" s="10" t="inlineStr">
         <is>
-          <t>갈락토미세스 / 발효여과물</t>
+          <t>갈락토미세스 · 발효여과물</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="E609" s="18" t="inlineStr">
         <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F609" s="18" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="F612" s="18" t="inlineStr">
         <is>
-          <t>아카시아 / 콜라겐, 콜라겐</t>
+          <t>아카시아 · 콜라겐, 콜라겐</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22323,7 @@
       </c>
       <c r="F613" s="18" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -22346,12 +22346,12 @@
       </c>
       <c r="E614" s="18" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F614" s="18" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -22374,12 +22374,12 @@
       </c>
       <c r="E615" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F615" s="18" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="F616" s="18" t="inlineStr">
         <is>
-          <t>레몬에센셜오일 등 / 원하는 에센셜오일</t>
+          <t>레몬에센셜오일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="E617" s="18" t="inlineStr">
         <is>
-          <t>장미향이 나는 나무 심지 / 를 수증기추출법으로 추출 / 몸과 마음을 진정, 베이스 노트</t>
+          <t>장미향이 나는 나무 심지 · 를 수증기추출법으로 추출 · 몸과 마음을 진정, 베이스 노트</t>
         </is>
       </c>
       <c r="F617" s="18" t="inlineStr">
@@ -22564,12 +22564,12 @@
       </c>
       <c r="E625" s="10" t="inlineStr">
         <is>
-          <t>세계적인 베스트셀러 E사의 갈색병 핵심성분, 비피더스균은 우리몸에 유익균 중 대표적인 균 중 하나입니다. / 지금까지는 장, 위 등을 위한 것이였지만 피부의 여러가지 문제점을 해결할 수있는 화장품원료로서 가치가 아주 높음. 고소한 발효향.</t>
+          <t>세계적인 베스트셀러 E사의 갈색병 핵심성분, 비피더스균은 우리몸에 유익균 중 대표적인 균 중 하나입니다. · 지금까지는 장, 위 등을 위한 것이였지만 피부의 여러가지 문제점을 해결할 수있는 화장품원료로서 가치가 아주 높음. 고소한 발효향.</t>
         </is>
       </c>
       <c r="F625" s="10" t="inlineStr">
         <is>
-          <t>갈락토미세스 / 발효여과물</t>
+          <t>갈락토미세스 · 발효여과물</t>
         </is>
       </c>
     </row>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="F626" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       </c>
       <c r="E627" s="10" t="inlineStr">
         <is>
-          <t>비타민류가 다량 함유 되어있는 / 샐러리, 양배추, 현미, 토마토, 다채, 당근, 브로컬리를 저온 추출법을 이용하여 비타민의 파괴를 최소화시켜 추출한 원료.</t>
+          <t>비타민류가 다량 함유 되어있는 · 샐러리, 양배추, 현미, 토마토, 다채, 당근, 브로컬리를 저온 추출법을 이용하여 비타민의 파괴를 최소화시켜 추출한 원료.</t>
         </is>
       </c>
       <c r="F627" s="10" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="F628" s="10" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, / 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀 · 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E629" s="10" t="inlineStr">
         <is>
-          <t>식약청인증 미백성분, 피부장벽강화, / 여드름관리 등</t>
+          <t>식약청인증 미백성분, 피부장벽강화 · 여드름관리 등</t>
         </is>
       </c>
       <c r="F629" s="10" t="inlineStr">
@@ -22878,12 +22878,12 @@
       </c>
       <c r="E639" s="18" t="inlineStr">
         <is>
-          <t>'바르는 보톡스' 등으로 인기, 2~4% 사용. / 독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. / 4%함유 제품을 하루에 두번, 28일간 사용 임상시 / 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득.</t>
+          <t>'바르는 보톡스' 등으로 인기, 2~4% 사용. · 독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. · 4%함유 제품을 하루에 두번, 28일간 사용 임상시 · 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득.</t>
         </is>
       </c>
       <c r="F639" s="18" t="inlineStr">
         <is>
-          <t>아데노신, / EGF등</t>
+          <t>아데노신 · EGF등</t>
         </is>
       </c>
     </row>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="F641" s="18" t="inlineStr">
         <is>
-          <t>아카시아 / 콜라겐, 콜라겐</t>
+          <t>아카시아 · 콜라겐, 콜라겐</t>
         </is>
       </c>
     </row>
@@ -22979,7 +22979,7 @@
       </c>
       <c r="F642" s="18" t="inlineStr">
         <is>
-          <t>FGF10/1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
+          <t>FGF10 · 1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -23038,7 +23038,7 @@
       </c>
       <c r="E644" s="18" t="inlineStr">
         <is>
-          <t>식약청 미백원료, 여드름, / 노화, 미백, 피부장벽강화</t>
+          <t>식약청 미백원료, 여드름 · 노화, 미백, 피부장벽강화</t>
         </is>
       </c>
       <c r="F644" s="18" t="inlineStr">
@@ -23283,10 +23283,10 @@
       </c>
       <c r="E656" s="10" t="inlineStr">
         <is>
-          <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
-        </is>
-      </c>
-      <c r="F656" s="10" t="n"/>
+          <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
+        </is>
+      </c>
+      <c r="F656" s="10" t="inlineStr"/>
     </row>
     <row r="657" ht="32" customHeight="1">
       <c r="A657" s="10" t="inlineStr">
@@ -23491,10 +23491,10 @@
       </c>
       <c r="E667" s="18" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F667" s="18" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F667" s="18" t="inlineStr"/>
     </row>
     <row r="668" ht="16" customHeight="1">
       <c r="A668" s="18" t="inlineStr">
@@ -23551,7 +23551,7 @@
       </c>
       <c r="E669" s="18" t="inlineStr">
         <is>
-          <t>천연 다당류 / (귀리, 효모, 버섯류, 해조류) / 피부 보습, 보호막 형성</t>
+          <t>천연 다당류 · (귀리, 효모, 버섯류, 해조류) · 피부 보습, 보호막 형성</t>
         </is>
       </c>
       <c r="F669" s="18" t="inlineStr">
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E670" s="18" t="inlineStr">
         <is>
-          <t>티로시나아제 억제를 통한 / 기미, 잡티, 색소침착 개선</t>
+          <t>티로시나아제 억제를 통한 · 기미, 잡티, 색소침착 개선</t>
         </is>
       </c>
       <c r="F670" s="18" t="inlineStr">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="F671" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="E682" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F682" s="10" t="inlineStr">
@@ -23867,10 +23867,10 @@
       </c>
       <c r="E683" s="10" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F683" s="10" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F683" s="10" t="inlineStr"/>
     </row>
     <row r="684" ht="32" customHeight="1">
       <c r="A684" s="10" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="E684" s="10" t="inlineStr">
         <is>
-          <t>티로시나아제 억제를 통한 / 기미, 잡티, 색소침착 개선</t>
+          <t>티로시나아제 억제를 통한 · 기미, 잡티, 색소침착 개선</t>
         </is>
       </c>
       <c r="F684" s="10" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="F685" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -24137,10 +24137,10 @@
       </c>
       <c r="E696" s="18" t="inlineStr">
         <is>
-          <t>가열 없이 유화, 점증 가능 / 점증, 유화, 지방산 복합 성분</t>
-        </is>
-      </c>
-      <c r="F696" s="18" t="n"/>
+          <t>가열 없이 유화, 점증 가능 · 점증, 유화, 지방산 복합 성분</t>
+        </is>
+      </c>
+      <c r="F696" s="18" t="inlineStr"/>
     </row>
     <row r="697" ht="32" customHeight="1">
       <c r="A697" s="18" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="F697" s="18" t="inlineStr">
         <is>
-          <t>로즈힙, / 스위트 아몬드오일</t>
+          <t>로즈힙 · 스위트 아몬드오일</t>
         </is>
       </c>
     </row>
@@ -24229,10 +24229,10 @@
       </c>
       <c r="E699" s="18" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F699" s="18" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F699" s="18" t="inlineStr"/>
     </row>
     <row r="700" ht="48" customHeight="1">
       <c r="A700" s="18" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="E700" s="18" t="inlineStr">
         <is>
-          <t>천연 다당류 / (귀리, 효모, 버섯류, 해조류) / 피부 보습, 보호막 형성</t>
+          <t>천연 다당류 · (귀리, 효모, 버섯류, 해조류) · 피부 보습, 보호막 형성</t>
         </is>
       </c>
       <c r="F700" s="18" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="F702" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -24516,7 +24516,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F712" s="10" t="n"/>
+      <c r="F712" s="10" t="inlineStr"/>
     </row>
     <row r="713" ht="14" customHeight="1">
       <c r="A713" s="13" t="inlineStr">
@@ -24663,7 +24663,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F721" s="18" t="n"/>
+      <c r="F721" s="18" t="inlineStr"/>
     </row>
     <row r="722" ht="32" customHeight="1">
       <c r="A722" s="18" t="inlineStr">
@@ -24693,7 +24693,7 @@
       </c>
       <c r="F722" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -24789,7 +24789,7 @@
       </c>
       <c r="F725" s="18" t="inlineStr">
         <is>
-          <t>아미노산17 컴플렉스, / 시카 엑소좀</t>
+          <t>아미노산17 컴플렉스 · 시카 엑소좀</t>
         </is>
       </c>
     </row>
@@ -24821,7 +24821,7 @@
       </c>
       <c r="F726" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="E735" s="10" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산, / 수분 레이어링으로 피부 겉과 속까지 수분 전달 / 수분충전부터 피부결까지 한 번에 해결 / 단독 사용 가능</t>
+          <t>크기가 다른 11가지 히아루론산 · 수분 레이어링으로 피부 겉과 속까지 수분 전달 · 수분충전부터 피부결까지 한 번에 해결 · 단독 사용 가능</t>
         </is>
       </c>
       <c r="F735" s="10" t="inlineStr">
@@ -24997,7 +24997,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F736" s="10" t="n"/>
+      <c r="F736" s="10" t="inlineStr"/>
     </row>
     <row r="737" ht="14" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
@@ -25156,7 +25156,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F745" s="18" t="n"/>
+      <c r="F745" s="18" t="inlineStr"/>
     </row>
     <row r="746" ht="32" customHeight="1">
       <c r="A746" s="18" t="inlineStr">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="F746" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -25282,7 +25282,7 @@
       </c>
       <c r="F749" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
           <t>사탕수수 채취, 점증제</t>
         </is>
       </c>
-      <c r="F759" s="10" t="n"/>
+      <c r="F759" s="10" t="inlineStr"/>
     </row>
     <row r="760" ht="48" customHeight="1">
       <c r="A760" s="10" t="inlineStr">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="F761" s="10" t="inlineStr">
         <is>
-          <t>아르간오일 2g, / 올리브리퀴드3g</t>
+          <t>아르간오일 2g · 올리브리퀴드3g</t>
         </is>
       </c>
     </row>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="F765" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -25686,7 +25686,7 @@
       </c>
       <c r="E766" s="10" t="inlineStr">
         <is>
-          <t>무향을 원하면 생략가능, / 네롤리, 일링일랑, 프랑킨센스, / 버가못FCF 블렌딩</t>
+          <t>무향을 원하면 생략가능 · 네롤리, 일링일랑, 프랑킨센스 · 버가못FCF 블렌딩</t>
         </is>
       </c>
       <c r="F766" s="10" t="inlineStr">
@@ -25868,7 +25868,7 @@
           <t>커피의 핵심 성분, 활력, 탄력</t>
         </is>
       </c>
-      <c r="F776" s="18" t="n"/>
+      <c r="F776" s="18" t="inlineStr"/>
     </row>
     <row r="777" ht="32" customHeight="1">
       <c r="A777" s="18" t="inlineStr">
@@ -25896,7 +25896,7 @@
           <t>연어DNA, 항염, 재생, PDRN(10만ppm)이 20% 고함량</t>
         </is>
       </c>
-      <c r="F777" s="18" t="n"/>
+      <c r="F777" s="18" t="inlineStr"/>
     </row>
     <row r="778" ht="32" customHeight="1">
       <c r="A778" s="18" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="F780" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -26146,7 +26146,7 @@
       </c>
       <c r="E789" s="10" t="inlineStr">
         <is>
-          <t>올리브오일에서 추출, / 가벼운 사용감, 빠른흡수</t>
+          <t>올리브오일에서 추출 · 가벼운 사용감, 빠른흡수</t>
         </is>
       </c>
       <c r="F789" s="10" t="inlineStr">
@@ -26219,7 +26219,7 @@
         </is>
       </c>
     </row>
-    <row r="792" ht="64" customHeight="1">
+    <row r="792" ht="48" customHeight="1">
       <c r="A792" s="10" t="inlineStr">
         <is>
           <t>프로바이오틱스 3</t>
@@ -26242,12 +26242,12 @@
       </c>
       <c r="E792" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, / 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물 · 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F792" s="10" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="E793" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 생긴 멜라닌 색소 발현 억제</t>
+          <t>비타민B3 · 생긴 멜라닌 색소 발현 억제</t>
         </is>
       </c>
       <c r="F793" s="10" t="inlineStr">
@@ -26343,7 +26343,7 @@
       </c>
       <c r="F795" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -26483,7 +26483,7 @@
       </c>
       <c r="E804" s="18" t="inlineStr">
         <is>
-          <t>올리브오일에서 추출, / 가벼운 사용감, 빠른흡수</t>
+          <t>올리브오일에서 추출 · 가벼운 사용감, 빠른흡수</t>
         </is>
       </c>
       <c r="F804" s="18" t="inlineStr">
@@ -26515,12 +26515,12 @@
       </c>
       <c r="E805" s="18" t="inlineStr">
         <is>
-          <t>마린 콜라겐 펩타이드, / 나이아신아마이드, 로즈워터 함유</t>
+          <t>마린 콜라겐 펩타이드 · 나이아신아마이드, 로즈워터 함유</t>
         </is>
       </c>
       <c r="F805" s="18" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -26669,7 +26669,7 @@
       </c>
       <c r="E814" s="10" t="inlineStr">
         <is>
-          <t>올리브오일에서 추출, / 가벼운 사용감, 빠른흡수</t>
+          <t>올리브오일에서 추출 · 가벼운 사용감, 빠른흡수</t>
         </is>
       </c>
       <c r="F814" s="10" t="inlineStr">
@@ -26706,7 +26706,7 @@
       </c>
       <c r="F815" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -26733,12 +26733,12 @@
       </c>
       <c r="E816" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F816" s="10" t="inlineStr">
         <is>
-          <t>비피다발효용해물, / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -26765,10 +26765,10 @@
       </c>
       <c r="E817" s="10" t="inlineStr">
         <is>
-          <t>세포간 신호 전달 메신저, / 재생, 탄력, 맑은 피부</t>
-        </is>
-      </c>
-      <c r="F817" s="10" t="n"/>
+          <t>세포간 신호 전달 메신저 · 재생, 탄력, 맑은 피부</t>
+        </is>
+      </c>
+      <c r="F817" s="10" t="inlineStr"/>
     </row>
     <row r="818" ht="32" customHeight="1">
       <c r="A818" s="10" t="inlineStr">
@@ -26793,10 +26793,10 @@
       </c>
       <c r="E818" s="10" t="inlineStr">
         <is>
-          <t>미백 효과 / 강력한 항산화 효과</t>
-        </is>
-      </c>
-      <c r="F818" s="10" t="n"/>
+          <t>미백 효과 · 강력한 항산화 효과</t>
+        </is>
+      </c>
+      <c r="F818" s="10" t="inlineStr"/>
     </row>
     <row r="819" ht="64" customHeight="1">
       <c r="A819" s="10" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="F819" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -26997,10 +26997,10 @@
       </c>
       <c r="E829" s="18" t="inlineStr">
         <is>
-          <t>실모양으로 캡슐화 / 저분자 콜라겐 + 히아루론산, 안전하게 피부까지</t>
-        </is>
-      </c>
-      <c r="F829" s="18" t="n"/>
+          <t>실모양으로 캡슐화 · 저분자 콜라겐 + 히아루론산, 안전하게 피부까지</t>
+        </is>
+      </c>
+      <c r="F829" s="18" t="inlineStr"/>
     </row>
     <row r="830" ht="48" customHeight="1">
       <c r="A830" s="18" t="inlineStr">
@@ -27025,7 +27025,7 @@
       </c>
       <c r="E830" s="18" t="inlineStr">
         <is>
-          <t>유기농 장미수(불가리아산) 함유, / 수분 공급, 진정, 겔타입으로 점증 역할</t>
+          <t>유기농 장미수(불가리아산) 함유 · 수분 공급, 진정, 겔타입으로 점증 역할</t>
         </is>
       </c>
       <c r="F830" s="18" t="inlineStr">
@@ -27092,7 +27092,7 @@
           <t>실제 피부 각질층 아미노산 구성과 유사한 17가지 아미노산, 보습·톤오버 유도·재생·톤업</t>
         </is>
       </c>
-      <c r="F832" s="18" t="n"/>
+      <c r="F832" s="18" t="inlineStr"/>
     </row>
     <row r="833" ht="48" customHeight="1">
       <c r="A833" s="18" t="inlineStr">
@@ -27116,7 +27116,7 @@
         </is>
       </c>
       <c r="E833" s="18">
-        <f>프로 판디올, 가볍지만 오래 가는 보습. / Non GMO 옥수수 유래, 히아루론산과 시너지</f>
+        <f>프로 판디올, 가볍지만 오래 가는 보습. · Non GMO 옥수수 유래, 히아루론산과 시너지</f>
         <v/>
       </c>
       <c r="F833" s="18" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="F834" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="E843" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F843" s="10" t="inlineStr">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="E844" s="10" t="inlineStr">
         <is>
-          <t>기미 개선효과가 뛰어난 트라넥사민산 / (을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
+          <t>기미 개선효과가 뛰어난 트라넥사민산 · (을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
       <c r="F844" s="10" t="inlineStr">
@@ -27377,7 +27377,7 @@
           <t>미백 효과 항산화 효과</t>
         </is>
       </c>
-      <c r="F845" s="10" t="n"/>
+      <c r="F845" s="10" t="inlineStr"/>
     </row>
     <row r="846" ht="32" customHeight="1">
       <c r="A846" s="10" t="inlineStr">
@@ -27437,7 +27437,7 @@
           <t>히비스커스꽃, 동백꽃, 샤프란꽃추출물 컴플렉스</t>
         </is>
       </c>
-      <c r="F847" s="10" t="n"/>
+      <c r="F847" s="10" t="inlineStr"/>
     </row>
     <row r="848" ht="32" customHeight="1">
       <c r="A848" s="10" t="inlineStr">
@@ -27499,7 +27499,7 @@
       </c>
       <c r="F849" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -27732,7 +27732,7 @@
       </c>
       <c r="E861" s="18" t="inlineStr">
         <is>
-          <t>기미 개선 효과가 뛰어난 트라넥사민산 / (을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
+          <t>기미 개선 효과가 뛰어난 트라넥사민산 · (을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
       <c r="F861" s="18" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>미백 효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F863" s="18" t="n"/>
+      <c r="F863" s="18" t="inlineStr"/>
     </row>
     <row r="864" ht="16" customHeight="1">
       <c r="A864" s="18" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="F866" s="18" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -27925,7 +27925,7 @@
       </c>
       <c r="F867" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -28087,10 +28087,10 @@
       </c>
       <c r="E876" s="10" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F876" s="10" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F876" s="10" t="inlineStr"/>
     </row>
     <row r="877" ht="32" customHeight="1">
       <c r="A877" s="10" t="inlineStr">
@@ -28115,12 +28115,12 @@
       </c>
       <c r="E877" s="10" t="inlineStr">
         <is>
-          <t>마린 콜라겐 펩타이드, 나이아신아마이드, / 로즈워터 함유</t>
+          <t>마린 콜라겐 펩타이드, 나이아신아마이드 · 로즈워터 함유</t>
         </is>
       </c>
       <c r="F877" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -28179,10 +28179,10 @@
       </c>
       <c r="E879" s="10" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F879" s="10" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F879" s="10" t="inlineStr"/>
     </row>
     <row r="880" ht="48" customHeight="1">
       <c r="A880" s="10" t="inlineStr">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="F880" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28244,7 @@
       </c>
       <c r="F881" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -28387,7 +28387,7 @@
       </c>
       <c r="E890" s="18" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산, / 수분 레이어링으로 피부 겉과 속까지 수분 전달 / 수분충전부터 피부결까지 한 번에 해결 / 단독 사용 가능</t>
+          <t>크기가 다른 11가지 히아루론산 · 수분 레이어링으로 피부 겉과 속까지 수분 전달 · 수분충전부터 피부결까지 한 번에 해결 · 단독 사용 가능</t>
         </is>
       </c>
       <c r="F890" s="18" t="inlineStr">
@@ -28415,10 +28415,10 @@
       </c>
       <c r="E891" s="18" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F891" s="18" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F891" s="18" t="inlineStr"/>
     </row>
     <row r="892" ht="14" customHeight="1">
       <c r="A892" s="15" t="inlineStr">
@@ -28598,10 +28598,10 @@
       </c>
       <c r="E900" s="10" t="inlineStr">
         <is>
-          <t>노벨상 받은 쑥, / 비타민 풍부, 진정</t>
-        </is>
-      </c>
-      <c r="F900" s="10" t="n"/>
+          <t>노벨상 받은 쑥 · 비타민 풍부, 진정</t>
+        </is>
+      </c>
+      <c r="F900" s="10" t="inlineStr"/>
     </row>
     <row r="901" ht="48" customHeight="1">
       <c r="A901" s="10" t="inlineStr">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="F901" s="10" t="inlineStr">
         <is>
-          <t>피비다발효용해물, / 사카로미세스발효여과물</t>
+          <t>피비다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -28658,7 +28658,7 @@
       </c>
       <c r="E902" s="10" t="inlineStr">
         <is>
-          <t>표피~진피 수분충전 / 고분자+중분자+저분자</t>
+          <t>표피~진피 수분충전 · 고분자+중분자+저분자</t>
         </is>
       </c>
       <c r="F902" s="10" t="inlineStr">
@@ -28690,7 +28690,7 @@
       </c>
       <c r="E903" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 기능성 고시원료</t>
+          <t>비타민B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F903" s="10" t="inlineStr">
@@ -28759,7 +28759,7 @@
       </c>
       <c r="F905" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
       </c>
       <c r="F906" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -28933,10 +28933,10 @@
       </c>
       <c r="E915" s="18" t="inlineStr">
         <is>
-          <t>노벨상 받은 쑥, / 비타민 풍부, 진정</t>
-        </is>
-      </c>
-      <c r="F915" s="18" t="n"/>
+          <t>노벨상 받은 쑥 · 비타민 풍부, 진정</t>
+        </is>
+      </c>
+      <c r="F915" s="18" t="inlineStr"/>
     </row>
     <row r="916" ht="32" customHeight="1">
       <c r="A916" s="18" t="inlineStr">
@@ -28961,7 +28961,7 @@
       </c>
       <c r="E916" s="18" t="inlineStr">
         <is>
-          <t>호호바오일 리포좀화, / 수상에 쉽게 분산</t>
+          <t>호호바오일 리포좀화 · 수상에 쉽게 분산</t>
         </is>
       </c>
       <c r="F916" s="18" t="inlineStr">
@@ -28993,7 +28993,7 @@
       </c>
       <c r="E917" s="18" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F917" s="18" t="inlineStr">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="F918" s="18" t="inlineStr">
         <is>
-          <t>피비다발효용해물, / 사카로미세스발효여과물</t>
+          <t>피비다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="E919" s="18" t="inlineStr">
         <is>
-          <t>비타민B3, / 식약처 기능성 고시원료</t>
+          <t>비타민B3 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F919" s="18" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="F920" s="18" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -29252,7 +29252,7 @@
         </is>
       </c>
     </row>
-    <row r="930" ht="32" customHeight="1">
+    <row r="930" ht="16" customHeight="1">
       <c r="A930" s="10" t="inlineStr">
         <is>
           <t>개똥쑥추출물</t>
@@ -29275,10 +29275,10 @@
       </c>
       <c r="E930" s="10" t="inlineStr">
         <is>
-          <t>노벨상 받은 쑥, / 진정, 항산화,</t>
-        </is>
-      </c>
-      <c r="F930" s="10" t="n"/>
+          <t>노벨상 받은 쑥 · 진정, 항산화</t>
+        </is>
+      </c>
+      <c r="F930" s="10" t="inlineStr"/>
     </row>
     <row r="931" ht="32" customHeight="1">
       <c r="A931" s="10" t="inlineStr">
@@ -29303,10 +29303,10 @@
       </c>
       <c r="E931" s="10" t="inlineStr">
         <is>
-          <t>올리브오일 지방산 함유, / O/W유화제</t>
-        </is>
-      </c>
-      <c r="F931" s="10" t="n"/>
+          <t>올리브오일 지방산 함유 · O · W유화제</t>
+        </is>
+      </c>
+      <c r="F931" s="10" t="inlineStr"/>
     </row>
     <row r="932" ht="32" customHeight="1">
       <c r="A932" s="10" t="inlineStr">
@@ -29331,7 +29331,7 @@
       </c>
       <c r="E932" s="10" t="inlineStr">
         <is>
-          <t>피지성분과비슷, / 빠른흡수</t>
+          <t>피지성분과비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F932" s="10" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="F934" s="10" t="inlineStr">
         <is>
-          <t>비피다발효용해물 / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -29464,7 +29464,7 @@
       </c>
       <c r="F936" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29496,7 @@
       </c>
       <c r="F937" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
